--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_25sep26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_25sep26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6402E7F9-959C-4854-A241-9EF986D14F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACCE829-2AD2-47E0-AE52-87C42E0382E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1142,7 +1142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1315,23 +1315,29 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1702,25 +1708,25 @@
         <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4">
-        <v>660</v>
+        <v>2470</v>
       </c>
       <c r="F2" s="4">
-        <v>-29.943742700000001</v>
+        <v>6.6586060969999998</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="H2" s="5">
-        <v>942.1</v>
+        <v>2315.8000000000002</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
@@ -1732,131 +1738,144 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B2, $C$2:$C$706, C2, $D$2:$D$706, D2, $E$2:$E$706, E2) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" ref="N2:N33" si="0">IF(COUNTIFS( $B$2:$B$706, B2, $C$2:$C$706, C2, $D$2:$D$706, D2, $E$2:$E$706, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O2" s="10"/>
+      <c r="P2" s="24"/>
     </row>
     <row r="3" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4">
-        <v>2560</v>
+        <v>2435</v>
       </c>
       <c r="F3" s="4">
-        <v>-22.85671237</v>
+        <v>5.1472493310000003</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="H3" s="5">
-        <v>3318.5</v>
+        <v>2315.8000000000002</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="36" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B3, $C$2:$C$706, C3, $D$2:$D$706, D3, $E$2:$E$706, E3) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
     </row>
     <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>62</v>
+      <c r="A4" s="3">
+        <v>46031.4375</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4">
-        <v>2660</v>
+        <v>1052</v>
       </c>
       <c r="F4" s="4">
-        <v>-19.843302699999999</v>
+        <v>4.6766169150000003</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="H4" s="5">
-        <v>3318.5</v>
+        <v>1005</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="36"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B4, $C$2:$C$706, C4, $D$2:$D$706, D4, $E$2:$E$706, E4) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="J4" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18">
+        <f>ABS((D4*E4)-L4)</f>
+        <v>3156</v>
+      </c>
+      <c r="N4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O4" s="10"/>
+      <c r="P4" s="19"/>
     </row>
     <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
-        <v>46252.688194444447</v>
+      <c r="A5" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4">
-        <v>136.15</v>
+        <v>281</v>
       </c>
       <c r="F5" s="4">
-        <v>-19.46646161</v>
+        <v>2.2934109939999998</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H5" s="5">
-        <v>169.06</v>
+        <v>274.7</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B5, $C$2:$C$706, C5, $D$2:$D$706, D5, $E$2:$E$706, E5) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O5" s="10"/>
+      <c r="P5" s="25"/>
     </row>
     <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
-        <v>46281.416666666664</v>
+        <v>46252.645138888889</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>282</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -1865,142 +1884,144 @@
         <v>10</v>
       </c>
       <c r="E6" s="4">
-        <v>706</v>
+        <v>401</v>
       </c>
       <c r="F6" s="4">
-        <v>-18.419228100000002</v>
+        <v>2.1135727019999999</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>289</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5">
-        <v>865.4</v>
+        <v>392.7</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="23" t="s">
+      <c r="J6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="L6" s="18">
-        <v>17940</v>
-      </c>
-      <c r="M6" s="18">
-        <f>ABS((D6*E6)-L6)</f>
-        <v>10880</v>
-      </c>
-      <c r="N6" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B6, $C$2:$C$706, C6, $D$2:$D$706, D6, $E$2:$E$706, E6) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" t="str">
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
     </row>
     <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>62</v>
+      <c r="A7" s="3">
+        <v>46275.457638888889</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E7" s="4">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="F7" s="4">
-        <v>-18.128654969999999</v>
+        <v>1.3976431899999999</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="H7" s="5">
-        <v>239.4</v>
+        <v>218.94</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B7, $C$2:$C$706, C7, $D$2:$D$706, D7, $E$2:$E$706, E7) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="K7" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="L7" s="18">
+        <v>56375</v>
+      </c>
+      <c r="M7" s="18">
+        <f>ABS((D7*E7)-L7)</f>
+        <v>34175</v>
+      </c>
+      <c r="N7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
     </row>
     <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4">
-        <v>2752</v>
+        <v>3888</v>
       </c>
       <c r="F8" s="4">
-        <v>-17.0709658</v>
+        <v>0.25786487879999997</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="H8" s="5">
-        <v>3318.5</v>
+        <v>3878</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="36" t="s">
-        <v>41</v>
-      </c>
+      <c r="J8" s="36"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B8, $C$2:$C$706, C8, $D$2:$D$706, D8, $E$2:$E$706, E8) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O8" s="25"/>
+      <c r="P8" s="10"/>
     </row>
     <row r="9" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
-        <v>46281.416666666664</v>
+        <v>46261.375</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>282</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E9" s="4">
-        <v>726</v>
+        <v>204</v>
       </c>
       <c r="F9" s="4">
-        <v>-16.108158079999999</v>
+        <v>-4.4098191969999999E-2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>289</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5">
-        <v>865.4</v>
+        <v>204.09</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
@@ -2009,267 +2030,289 @@
         <v>41</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>284</v>
+        <v>185</v>
       </c>
       <c r="L9" s="18">
-        <v>17940</v>
+        <v>10550</v>
       </c>
       <c r="M9" s="18">
         <f>ABS((D9*E9)-L9)</f>
-        <v>10680</v>
+        <v>350</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B9, $C$2:$C$706, C9, $D$2:$D$706, D9, $E$2:$E$706, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
     </row>
     <row r="10" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="A10" s="31">
+        <v>46288.375</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="4">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4">
-        <v>701</v>
+      <c r="D10" s="33">
+        <v>10</v>
+      </c>
+      <c r="E10" s="33">
+        <v>887</v>
       </c>
       <c r="F10" s="4">
-        <v>-14.73056806</v>
+        <v>-0.1069880061</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="H10" s="5">
-        <v>822.1</v>
+        <v>887.95</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B10, $C$2:$C$706, C10, $D$2:$D$706, D10, $E$2:$E$706, E10) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="J10" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="L10" s="28">
+        <v>9170</v>
+      </c>
+      <c r="M10" s="28">
+        <f>ABS((D10*E10)-L10)</f>
+        <v>300</v>
+      </c>
+      <c r="N10" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v>Duplicate</v>
+      </c>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
     </row>
     <row r="11" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="A11" s="31">
+        <v>46288.375</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>3914</v>
+      <c r="D11" s="33">
+        <v>10</v>
+      </c>
+      <c r="E11" s="33">
+        <v>887</v>
       </c>
       <c r="F11" s="4">
-        <v>-14.14783944</v>
+        <v>-0.1069880061</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="H11" s="5">
-        <v>4559</v>
+        <v>887.95</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B11, $C$2:$C$706, C11, $D$2:$D$706, D11, $E$2:$E$706, E11) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="J11" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="L11" s="28">
+        <v>9070</v>
+      </c>
+      <c r="M11" s="28">
+        <f>ABS((D11*E11)-L11)</f>
+        <v>200</v>
+      </c>
+      <c r="N11" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v>Duplicate</v>
+      </c>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
     </row>
     <row r="12" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>561</v>
+        <v>3856</v>
       </c>
       <c r="F12" s="4">
-        <v>-14.08882083</v>
+        <v>-0.56730273340000004</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="H12" s="5">
-        <v>653</v>
+        <v>3878</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="36" t="s">
-        <v>41</v>
-      </c>
+      <c r="J12" s="36"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B12, $C$2:$C$706, C12, $D$2:$D$706, D12, $E$2:$E$706, E12) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O12" s="19"/>
+      <c r="P12" s="10"/>
     </row>
     <row r="13" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
-        <v>46252.635416666664</v>
+        <v>46282.416666666664</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="4">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E13" s="4">
-        <v>2892</v>
+        <v>880</v>
       </c>
       <c r="F13" s="4">
-        <v>-12.852192260000001</v>
+        <v>-0.89532068249999996</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="H13" s="5">
-        <v>3318.5</v>
+        <v>887.95</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
+      <c r="J13" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="L13" s="18">
+        <v>35920</v>
+      </c>
+      <c r="M13" s="18">
+        <f>ABS((D13*E13)-L13)</f>
+        <v>720</v>
+      </c>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B13, $C$2:$C$706, C13, $D$2:$D$706, D13, $E$2:$E$706, E13) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
     </row>
     <row r="14" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
-        <v>62</v>
+      <c r="A14" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4">
-        <v>4014</v>
+        <v>1302</v>
       </c>
       <c r="F14" s="4">
-        <v>-11.95437596</v>
+        <v>-1.138952164</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="H14" s="5">
-        <v>4559</v>
+        <v>1317</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="36"/>
+      <c r="J14" s="36" t="s">
+        <v>41</v>
+      </c>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B14, $C$2:$C$706, C14, $D$2:$D$706, D14, $E$2:$E$706, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="15" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
-        <v>46288.479861111111</v>
+        <v>46252.6875</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E15" s="4">
-        <v>580</v>
+        <v>326</v>
       </c>
       <c r="F15" s="4">
-        <v>-11.179173049999999</v>
+        <v>-1.212121212</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="H15" s="5">
-        <v>653</v>
+        <v>330</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="23" t="s">
+      <c r="J15" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="K15" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="L15" s="18">
-        <v>3150</v>
-      </c>
-      <c r="M15" s="18">
-        <f>ABS((D15*E15)-L15)</f>
-        <v>250</v>
-      </c>
-      <c r="N15" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B15, $C$2:$C$706, C15, $D$2:$D$706, D15, $E$2:$E$706, E15) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="16" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3">
-        <v>46287.375</v>
+      <c r="A16" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>291</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>10</v>
@@ -2278,122 +2321,126 @@
         <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>1564</v>
+        <v>3830</v>
       </c>
       <c r="F16" s="4">
-        <v>-11.16160182</v>
+        <v>-1.237751418</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>293</v>
+        <v>50</v>
       </c>
       <c r="H16" s="5">
-        <v>1760.5</v>
+        <v>3878</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="L16" s="18">
-        <v>3430</v>
-      </c>
-      <c r="M16" s="18">
-        <f>ABS((D16*E16)-L16)</f>
-        <v>302</v>
-      </c>
-      <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B16, $C$2:$C$706, C16, $D$2:$D$706, D16, $E$2:$E$706, E16) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="J16" s="36"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" t="str">
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
     </row>
     <row r="17" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
-        <v>62</v>
+      <c r="A17" s="3">
+        <v>46260.375</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="4">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="E17" s="4">
-        <v>111</v>
+        <v>2348</v>
       </c>
       <c r="F17" s="4">
-        <v>-10.77170418</v>
+        <v>-1.327954278</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H17" s="5">
-        <v>124.4</v>
+        <v>2379.6</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
+      <c r="J17" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="L17" s="18">
+        <v>7344</v>
+      </c>
+      <c r="M17" s="18">
+        <f>ABS((D17*E17)-L17)</f>
+        <v>300</v>
+      </c>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B17, $C$2:$C$706, C17, $D$2:$D$706, D17, $E$2:$E$706, E17) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
     </row>
     <row r="18" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E18" s="4">
-        <v>1751</v>
+        <v>201</v>
       </c>
       <c r="F18" s="4">
-        <v>-10.112936339999999</v>
+        <v>-1.5140379239999999</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="H18" s="5">
-        <v>1948</v>
+        <v>204.09</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="36"/>
+      <c r="J18" s="37" t="s">
+        <v>41</v>
+      </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B18, $C$2:$C$706, C18, $D$2:$D$706, D18, $E$2:$E$706, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18"/>
       <c r="P18"/>
     </row>
     <row r="19" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
-        <v>62</v>
+      <c r="A19" s="3">
+        <v>46287.375</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
@@ -2402,236 +2449,259 @@
         <v>1</v>
       </c>
       <c r="E19" s="4">
-        <v>4164</v>
+        <v>19300</v>
       </c>
       <c r="F19" s="4">
-        <v>-8.6641807409999991</v>
+        <v>-1.580826109</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H19" s="5">
-        <v>4559</v>
+        <v>19610</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="36"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B19, $C$2:$C$706, C19, $D$2:$D$706, D19, $E$2:$E$706, E19) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O19"/>
-      <c r="P19"/>
+      <c r="J19" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="L19" s="18">
+        <v>19950</v>
+      </c>
+      <c r="M19" s="18">
+        <f>ABS((D19*E19)-L19)</f>
+        <v>650</v>
+      </c>
+      <c r="N19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="54">
-        <v>46289.375</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="A20" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="5">
-        <v>5</v>
-      </c>
-      <c r="E20" s="5">
-        <v>601</v>
+      <c r="D20" s="4">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4">
+        <v>3810</v>
       </c>
       <c r="F20" s="4">
-        <v>-7.9632465540000004</v>
+        <v>-1.753481176</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="H20" s="5">
-        <v>653</v>
+        <v>3878</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="L20" s="18">
-        <v>3245</v>
-      </c>
-      <c r="M20" s="18">
-        <f>ABS((D20*E20)-L20)</f>
-        <v>240</v>
-      </c>
-      <c r="N20" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B20, $C$2:$C$706, C20, $D$2:$D$706, D20, $E$2:$E$706, E20) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="J20" s="36"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" t="str">
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
-        <v>62</v>
+      <c r="A21" s="3">
+        <v>46283.375</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E21" s="4">
-        <v>18052</v>
+        <v>870.2</v>
       </c>
       <c r="F21" s="4">
-        <v>-7.9449260580000001</v>
+        <v>-1.7832957110000001</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H21" s="5">
-        <v>19610</v>
+        <v>886</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B21, $C$2:$C$706, C21, $D$2:$D$706, D21, $E$2:$E$706, E21) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O21"/>
-      <c r="P21"/>
+      <c r="J21" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="L21" s="18">
+        <v>17920</v>
+      </c>
+      <c r="M21" s="18">
+        <f>ABS((D21*E21)-L21)</f>
+        <v>516</v>
+      </c>
+      <c r="N21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
-        <v>62</v>
+      <c r="A22" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E22" s="4">
-        <v>4415</v>
+        <v>870</v>
       </c>
       <c r="F22" s="4">
-        <v>-7.9306821259999998</v>
+        <v>-1.8058690740000001</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="H22" s="5">
-        <v>4795.3</v>
+        <v>886</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="36"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B22, $C$2:$C$706, C22, $D$2:$D$706, D22, $E$2:$E$706, E22) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O22"/>
-      <c r="P22"/>
+      <c r="J22" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="L22" s="18">
+        <v>17700</v>
+      </c>
+      <c r="M22" s="18">
+        <f>ABS((D22*E22)-L22)</f>
+        <v>300</v>
+      </c>
+      <c r="N22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="P22" s="24"/>
     </row>
     <row r="23" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4">
-        <v>115.25</v>
+        <v>6920</v>
       </c>
       <c r="F23" s="4">
-        <v>-7.3553054659999999</v>
+        <v>-1.8439716310000001</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="H23" s="5">
-        <v>124.4</v>
+        <v>7050</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="36"/>
+      <c r="J23" s="22" t="s">
+        <v>55</v>
+      </c>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B23, $C$2:$C$706, C23, $D$2:$D$706, D23, $E$2:$E$706, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
       <c r="P23"/>
     </row>
     <row r="24" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
-        <v>62</v>
+      <c r="A24" s="3">
+        <v>46286.375</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" s="4">
-        <v>4456</v>
+        <v>712</v>
       </c>
       <c r="F24" s="4">
-        <v>-7.0756782679999999</v>
+        <v>-1.9283746559999999</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="H24" s="5">
-        <v>4795.3</v>
+        <v>726</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="36"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B24, $C$2:$C$706, C24, $D$2:$D$706, D24, $E$2:$E$706, E24) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O24"/>
-      <c r="P24"/>
+      <c r="J24" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="L24" s="18">
+        <f>7470/2</f>
+        <v>3735</v>
+      </c>
+      <c r="M24" s="18">
+        <f>ABS((D24*E24)-L24)</f>
+        <v>175</v>
+      </c>
+      <c r="N24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
-        <v>62</v>
+      <c r="A25" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>20</v>
@@ -2640,13 +2710,13 @@
         <v>10</v>
       </c>
       <c r="D25" s="4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E25" s="4">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F25" s="4">
-        <v>-6.7524115760000001</v>
+        <v>-1.9292604499999999</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>86</v>
@@ -2657,102 +2727,112 @@
       <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="36"/>
+      <c r="J25" s="37" t="s">
+        <v>41</v>
+      </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B25, $C$2:$C$706, C25, $D$2:$D$706, D25, $E$2:$E$706, E25) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O25"/>
-      <c r="P25"/>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
-        <v>62</v>
+      <c r="A26" s="3">
+        <v>46286.375</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" s="4">
-        <v>411</v>
+        <v>1664</v>
       </c>
       <c r="F26" s="4">
-        <v>-6.5909090910000003</v>
+        <v>-1.9446081319999999</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="H26" s="5">
-        <v>440</v>
+        <v>1697</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="36"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B26, $C$2:$C$706, C26, $D$2:$D$706, D26, $E$2:$E$706, E26) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O26"/>
-      <c r="P26"/>
+      <c r="J26" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="L26" s="18">
+        <v>8970</v>
+      </c>
+      <c r="M26" s="18">
+        <f>ABS((D26*E26)-L26)</f>
+        <v>650</v>
+      </c>
+      <c r="N26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
-        <v>46254.375</v>
+        <v>46288.569444444445</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E27" s="4">
-        <v>2230</v>
+        <v>1136</v>
       </c>
       <c r="F27" s="4">
-        <v>-6.2867708860000002</v>
+        <v>-2.1785929560000001</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="H27" s="5">
-        <v>2379.6</v>
+        <v>1161.3</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="65" t="s">
+      <c r="J27" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K27" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
+      <c r="K27" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="L27" s="18">
+        <v>11660</v>
+      </c>
+      <c r="M27" s="18">
+        <f>ABS((D27*E27)-L27)</f>
+        <v>300</v>
+      </c>
       <c r="N27" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B27, $C$2:$C$706, C27, $D$2:$D$706, D27, $E$2:$E$706, E27) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O27"/>
-      <c r="P27"/>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="28" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="6" t="s">
-        <v>62</v>
+      <c r="A28" s="3">
+        <v>46268.385416666664</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>19</v>
@@ -2761,13 +2841,13 @@
         <v>10</v>
       </c>
       <c r="D28" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E28" s="4">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F28" s="4">
-        <v>-5.910295058</v>
+        <v>-2.2563259339999999</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>40</v>
@@ -2778,134 +2858,147 @@
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B28, $C$2:$C$706, C28, $D$2:$D$706, D28, $E$2:$E$706, E28) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O28"/>
-      <c r="P28"/>
+      <c r="J28" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="L28" s="18">
+        <v>21900</v>
+      </c>
+      <c r="M28" s="18">
+        <f>ABS((D28*E28)-L28)</f>
+        <v>500</v>
+      </c>
+      <c r="N28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
     </row>
     <row r="29" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="6" t="s">
-        <v>62</v>
+      <c r="A29" s="3">
+        <v>46288.5</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="4">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E29" s="4">
-        <v>836</v>
+        <v>321</v>
       </c>
       <c r="F29" s="4">
-        <v>-5.6433408580000002</v>
+        <v>-2.7272727269999999</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="H29" s="5">
-        <v>886</v>
+        <v>330</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B29, $C$2:$C$706, C29, $D$2:$D$706, D29, $E$2:$E$706, E29) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O29"/>
-      <c r="P29"/>
+      <c r="J29" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="L29" s="18">
+        <v>32800</v>
+      </c>
+      <c r="M29" s="18">
+        <f>ABS((D29*E29)-L29)</f>
+        <v>700</v>
+      </c>
+      <c r="N29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="4">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E30" s="4">
-        <v>401</v>
+        <v>4010</v>
       </c>
       <c r="F30" s="4">
-        <v>-5.4468285779999999</v>
+        <v>-2.905569007</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H30" s="5">
-        <v>424.1</v>
+        <v>4130</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J30" s="22" t="s">
-        <v>55</v>
+      <c r="J30" s="36" t="s">
+        <v>41</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B30, $C$2:$C$706, C30, $D$2:$D$706, D30, $E$2:$E$706, E30) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O30"/>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E31" s="4">
-        <v>18552</v>
+        <v>862</v>
       </c>
       <c r="F31" s="4">
-        <v>-5.395206527</v>
+        <v>-2.9224618499999999</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="H31" s="5">
-        <v>19610</v>
+        <v>887.95</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J31" s="36"/>
+      <c r="J31" s="36" t="s">
+        <v>55</v>
+      </c>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B31, $C$2:$C$706, C31, $D$2:$D$706, D31, $E$2:$E$706, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -2916,25 +3009,25 @@
         <v>62</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="E32" s="4">
-        <v>4560</v>
+        <v>1277</v>
       </c>
       <c r="F32" s="4">
-        <v>-4.9068879939999999</v>
+        <v>-3.037205771</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="H32" s="5">
-        <v>4795.3</v>
+        <v>1317</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
@@ -2944,194 +3037,180 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B32, $C$2:$C$706, C32, $D$2:$D$706, D32, $E$2:$E$706, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
       <c r="P32"/>
     </row>
     <row r="33" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="3">
-        <v>46121.375</v>
+      <c r="A33" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
-        <v>1614</v>
+        <v>3760</v>
       </c>
       <c r="F33" s="4">
-        <v>-4.8909840899999999</v>
+        <v>-3.0428055700000001</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="H33" s="5">
-        <v>1697</v>
+        <v>3878</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="K33" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="L33" s="18">
-        <f>3*1794</f>
-        <v>5382</v>
-      </c>
-      <c r="M33" s="18">
-        <f>ABS((D33*E33)-L33)</f>
-        <v>540</v>
-      </c>
-      <c r="N33" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B33, $C$2:$C$706, C33, $D$2:$D$706, D33, $E$2:$E$706, E33) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="J33" s="36"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" t="str">
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
-      <c r="P33"/>
     </row>
     <row r="34" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="3">
-        <v>46258.601388888892</v>
+      <c r="A34" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E34" s="4">
-        <v>2271</v>
+        <v>212</v>
       </c>
       <c r="F34" s="4">
-        <v>-4.5637922340000001</v>
+        <v>-3.1698182149999998</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="H34" s="5">
-        <v>2379.6</v>
+        <v>218.94</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J34" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="K34" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="L34" s="18">
-        <v>7113</v>
-      </c>
-      <c r="M34" s="18">
-        <f>ABS((D34*E34)-L34)</f>
-        <v>300</v>
-      </c>
-      <c r="N34" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B34, $C$2:$C$706, C34, $D$2:$D$706, D34, $E$2:$E$706, E34) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O34"/>
-      <c r="P34"/>
+      <c r="J34" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" t="str">
+        <f t="shared" ref="N34:N65" si="1">IF(COUNTIFS( $B$2:$B$706, B34, $C$2:$C$706, C34, $D$2:$D$706, D34, $E$2:$E$706, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="35" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="3">
-        <v>46252.688194444447</v>
+      <c r="A35" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E35" s="4">
-        <v>640</v>
+        <v>4410</v>
       </c>
       <c r="F35" s="4">
-        <v>-4.3491256910000002</v>
+        <v>-3.268260583</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="H35" s="5">
-        <v>669.1</v>
+        <v>4559</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="36" t="s">
-        <v>41</v>
-      </c>
+      <c r="J35" s="36"/>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B35, $C$2:$C$706, C35, $D$2:$D$706, D35, $E$2:$E$706, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
       <c r="P35"/>
     </row>
     <row r="36" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="6" t="s">
-        <v>62</v>
+      <c r="A36" s="3">
+        <v>46286.527083333334</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E36" s="4">
-        <v>119</v>
+        <v>4410</v>
       </c>
       <c r="F36" s="4">
-        <v>-4.3408360129999997</v>
+        <v>-3.268260583</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H36" s="5">
-        <v>124.4</v>
+        <v>4559</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="36"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B36, $C$2:$C$706, C36, $D$2:$D$706, D36, $E$2:$E$706, E36) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O36"/>
+      <c r="J36" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="L36" s="18">
+        <v>4724</v>
+      </c>
+      <c r="M36" s="18">
+        <f>ABS((D36*E36)-L36)</f>
+        <v>314</v>
+      </c>
+      <c r="N36" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="37" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="6" t="s">
-        <v>62</v>
+      <c r="A37" s="3">
+        <v>46286.375</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>10</v>
@@ -3140,69 +3219,75 @@
         <v>5</v>
       </c>
       <c r="E37" s="4">
-        <v>1614</v>
+        <v>702</v>
       </c>
       <c r="F37" s="4">
-        <v>-4.3272080620000004</v>
+        <v>-3.3057851239999998</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="H37" s="5">
-        <v>1687</v>
+        <v>726</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="22" t="s">
+      <c r="J37" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B37, $C$2:$C$706, C37, $D$2:$D$706, D37, $E$2:$E$706, E37) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O37"/>
-      <c r="P37"/>
+      <c r="K37" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="L37" s="18">
+        <f>7470/2</f>
+        <v>3735</v>
+      </c>
+      <c r="M37" s="18">
+        <f>ABS((D37*E37)-L37)</f>
+        <v>225</v>
+      </c>
+      <c r="N37" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="38" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E38" s="4">
-        <v>4364</v>
+        <v>196</v>
       </c>
       <c r="F38" s="4">
-        <v>-4.277253784</v>
+        <v>-3.9639374790000002</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="H38" s="5">
-        <v>4559</v>
+        <v>204.09</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J38" s="37" t="s">
+      <c r="J38" s="36" t="s">
         <v>41</v>
       </c>
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B38, $C$2:$C$706, C38, $D$2:$D$706, D38, $E$2:$E$706, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -3243,7 +3328,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B39, $C$2:$C$706, C39, $D$2:$D$706, D39, $E$2:$E$706, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P39"/>
@@ -3253,48 +3338,48 @@
         <v>62</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E40" s="4">
-        <v>196</v>
+        <v>4364</v>
       </c>
       <c r="F40" s="4">
-        <v>-3.9639374790000002</v>
+        <v>-4.277253784</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="H40" s="5">
-        <v>204.09</v>
+        <v>4559</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J40" s="36" t="s">
+      <c r="J40" s="37" t="s">
         <v>41</v>
       </c>
       <c r="K40" s="17"/>
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B40, $C$2:$C$706, C40, $D$2:$D$706, D40, $E$2:$E$706, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
       <c r="P40"/>
     </row>
     <row r="41" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="3">
-        <v>46286.375</v>
+      <c r="A41" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>10</v>
@@ -3303,63 +3388,57 @@
         <v>5</v>
       </c>
       <c r="E41" s="4">
-        <v>702</v>
+        <v>1614</v>
       </c>
       <c r="F41" s="4">
-        <v>-3.3057851239999998</v>
+        <v>-4.3272080620000004</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="H41" s="5">
-        <v>726</v>
+        <v>1687</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="23" t="s">
+      <c r="J41" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="K41" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="L41" s="18">
-        <f>7470/2</f>
-        <v>3735</v>
-      </c>
-      <c r="M41" s="18">
-        <f>ABS((D41*E41)-L41)</f>
-        <v>225</v>
-      </c>
-      <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B41, $C$2:$C$706, C41, $D$2:$D$706, D41, $E$2:$E$706, E41) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O41"/>
+      <c r="P41"/>
     </row>
     <row r="42" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E42" s="4">
-        <v>4410</v>
+        <v>119</v>
       </c>
       <c r="F42" s="4">
-        <v>-3.268260583</v>
+        <v>-4.3408360129999997</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H42" s="5">
-        <v>4559</v>
+        <v>124.4</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>8</v>
@@ -3369,160 +3448,174 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B42, $C$2:$C$706, C42, $D$2:$D$706, D42, $E$2:$E$706, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
-      <c r="P42"/>
+      <c r="P42" s="10"/>
     </row>
     <row r="43" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="3">
-        <v>46286.527083333334</v>
+        <v>46252.688194444447</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E43" s="4">
-        <v>4410</v>
+        <v>640</v>
       </c>
       <c r="F43" s="4">
-        <v>-3.268260583</v>
+        <v>-4.3491256910000002</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H43" s="5">
-        <v>4559</v>
+        <v>669.1</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="23" t="s">
+      <c r="J43" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="K43" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="L43" s="18">
-        <v>4724</v>
-      </c>
-      <c r="M43" s="18">
-        <f>ABS((D43*E43)-L43)</f>
-        <v>314</v>
-      </c>
-      <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B43, $C$2:$C$706, C43, $D$2:$D$706, D43, $E$2:$E$706, E43) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O43"/>
+      <c r="P43"/>
     </row>
     <row r="44" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="6" t="s">
-        <v>62</v>
+      <c r="A44" s="3">
+        <v>46258.601388888892</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E44" s="4">
-        <v>212</v>
+        <v>2271</v>
       </c>
       <c r="F44" s="4">
-        <v>-3.1698182149999998</v>
+        <v>-4.5637922340000001</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="H44" s="5">
-        <v>218.94</v>
+        <v>2379.6</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B44, $C$2:$C$706, C44, $D$2:$D$706, D44, $E$2:$E$706, E44) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="J44" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="L44" s="18">
+        <v>7113</v>
+      </c>
+      <c r="M44" s="18">
+        <f>ABS((D44*E44)-L44)</f>
+        <v>300</v>
+      </c>
+      <c r="N44" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O44"/>
+      <c r="P44"/>
     </row>
     <row r="45" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="6" t="s">
-        <v>62</v>
+      <c r="A45" s="3">
+        <v>46121.375</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" s="4">
-        <v>3760</v>
+        <v>1614</v>
       </c>
       <c r="F45" s="4">
-        <v>-3.0428055700000001</v>
+        <v>-4.8909840899999999</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="H45" s="5">
-        <v>3878</v>
+        <v>1697</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="36"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B45, $C$2:$C$706, C45, $D$2:$D$706, D45, $E$2:$E$706, E45) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="J45" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="L45" s="18">
+        <f>3*1794</f>
+        <v>5382</v>
+      </c>
+      <c r="M45" s="18">
+        <f>ABS((D45*E45)-L45)</f>
+        <v>540</v>
+      </c>
+      <c r="N45" s="10" t="str">
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
-      <c r="P45" s="10"/>
+      <c r="P45"/>
     </row>
     <row r="46" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="4">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="E46" s="4">
-        <v>1277</v>
+        <v>4560</v>
       </c>
       <c r="F46" s="4">
-        <v>-3.037205771</v>
+        <v>-4.9068879939999999</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="H46" s="5">
-        <v>1317</v>
+        <v>4795.3</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>8</v>
@@ -3532,7 +3625,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B46, $C$2:$C$706, C46, $D$2:$D$706, D46, $E$2:$E$706, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -3543,37 +3636,35 @@
         <v>62</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="4">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E47" s="4">
-        <v>862</v>
+        <v>18552</v>
       </c>
       <c r="F47" s="4">
-        <v>-2.9224618499999999</v>
+        <v>-5.395206527</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="H47" s="5">
-        <v>887.95</v>
+        <v>19610</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="36" t="s">
-        <v>55</v>
-      </c>
+      <c r="J47" s="36"/>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B47, $C$2:$C$706, C47, $D$2:$D$706, D47, $E$2:$E$706, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -3584,89 +3675,85 @@
         <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="4">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E48" s="4">
-        <v>4010</v>
+        <v>401</v>
       </c>
       <c r="F48" s="4">
-        <v>-2.905569007</v>
+        <v>-5.4468285779999999</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H48" s="5">
-        <v>4130</v>
+        <v>424.1</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="36" t="s">
-        <v>41</v>
+      <c r="J48" s="22" t="s">
+        <v>55</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B48, $C$2:$C$706, C48, $D$2:$D$706, D48, $E$2:$E$706, E48) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O48"/>
     </row>
     <row r="49" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="3">
-        <v>46288.5</v>
+      <c r="A49" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="4">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E49" s="4">
-        <v>321</v>
+        <v>836</v>
       </c>
       <c r="F49" s="4">
-        <v>-2.7272727269999999</v>
+        <v>-5.6433408580000002</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="H49" s="5">
-        <v>330</v>
+        <v>886</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J49" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="K49" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="L49" s="18">
-        <v>32800</v>
-      </c>
-      <c r="M49" s="18">
-        <f>ABS((D49*E49)-L49)</f>
-        <v>700</v>
-      </c>
-      <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B49, $C$2:$C$706, C49, $D$2:$D$706, D49, $E$2:$E$706, E49) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="J49" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O49"/>
+      <c r="P49"/>
     </row>
     <row r="50" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="3">
-        <v>46268.385416666664</v>
+      <c r="A50" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>19</v>
@@ -3675,13 +3762,13 @@
         <v>10</v>
       </c>
       <c r="D50" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E50" s="4">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F50" s="4">
-        <v>-2.2563259339999999</v>
+        <v>-5.910295058</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>40</v>
@@ -3692,119 +3779,104 @@
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="K50" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="L50" s="18">
-        <v>21900</v>
-      </c>
-      <c r="M50" s="18">
-        <f>ABS((D50*E50)-L50)</f>
-        <v>500</v>
-      </c>
-      <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B50, $C$2:$C$706, C50, $D$2:$D$706, D50, $E$2:$E$706, E50) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="J50" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O50"/>
+      <c r="P50"/>
     </row>
     <row r="51" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
-        <v>46288.569444444445</v>
+        <v>46254.375</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D51" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E51" s="4">
-        <v>1136</v>
+        <v>2230</v>
       </c>
       <c r="F51" s="4">
-        <v>-2.1785929560000001</v>
+        <v>-6.2867708860000002</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="H51" s="5">
-        <v>1161.3</v>
+        <v>2379.6</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="23" t="s">
+      <c r="J51" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="K51" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="L51" s="18">
-        <v>11660</v>
-      </c>
-      <c r="M51" s="18">
-        <f>ABS((D51*E51)-L51)</f>
-        <v>300</v>
-      </c>
+      <c r="K51" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B51, $C$2:$C$706, C51, $D$2:$D$706, D51, $E$2:$E$706, E51) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O51"/>
+      <c r="P51"/>
     </row>
     <row r="52" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="3">
-        <v>46286.375</v>
+      <c r="A52" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E52" s="4">
-        <v>1664</v>
+        <v>411</v>
       </c>
       <c r="F52" s="4">
-        <v>-1.9446081319999999</v>
+        <v>-6.5909090910000003</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="H52" s="5">
-        <v>1697</v>
+        <v>440</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="K52" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="L52" s="18">
-        <v>8970</v>
-      </c>
-      <c r="M52" s="18">
-        <f>ABS((D52*E52)-L52)</f>
-        <v>650</v>
-      </c>
-      <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B52, $C$2:$C$706, C52, $D$2:$D$706, D52, $E$2:$E$706, E52) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="J52" s="36"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O52"/>
+      <c r="P52"/>
     </row>
     <row r="53" spans="1:16" s="24" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="3">
-        <v>46252.6875</v>
+      <c r="A53" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>20</v>
@@ -3813,13 +3885,13 @@
         <v>10</v>
       </c>
       <c r="D53" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E53" s="4">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F53" s="4">
-        <v>-1.9292604499999999</v>
+        <v>-6.7524115760000001</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>86</v>
@@ -3830,249 +3902,225 @@
       <c r="I53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J53" s="37" t="s">
-        <v>41</v>
-      </c>
+      <c r="J53" s="36"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B53, $C$2:$C$706, C53, $D$2:$D$706, D53, $E$2:$E$706, E53) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O53"/>
+      <c r="P53"/>
     </row>
     <row r="54" spans="1:16" s="30" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="3">
-        <v>46286.375</v>
+      <c r="A54" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E54" s="4">
-        <v>712</v>
+        <v>4456</v>
       </c>
       <c r="F54" s="4">
-        <v>-1.9283746559999999</v>
+        <v>-7.0756782679999999</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="H54" s="5">
-        <v>726</v>
+        <v>4795.3</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="K54" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="L54" s="18">
-        <f>7470/2</f>
-        <v>3735</v>
-      </c>
-      <c r="M54" s="18">
-        <f>ABS((D54*E54)-L54)</f>
-        <v>175</v>
-      </c>
-      <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B54, $C$2:$C$706, C54, $D$2:$D$706, D54, $E$2:$E$706, E54) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-    </row>
-    <row r="55" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J54" s="36"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O54"/>
+      <c r="P54"/>
+    </row>
+    <row r="55" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E55" s="4">
-        <v>6920</v>
+        <v>115.25</v>
       </c>
       <c r="F55" s="4">
-        <v>-1.8439716310000001</v>
+        <v>-7.3553054659999999</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="H55" s="5">
-        <v>7050</v>
+        <v>124.4</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J55" s="22" t="s">
-        <v>55</v>
-      </c>
+      <c r="J55" s="36"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B55, $C$2:$C$706, C55, $D$2:$D$706, D55, $E$2:$E$706, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
       <c r="P55"/>
     </row>
     <row r="56" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="3">
-        <v>46261.375</v>
+      <c r="A56" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E56" s="4">
-        <v>870</v>
+        <v>4415</v>
       </c>
       <c r="F56" s="4">
-        <v>-1.8058690740000001</v>
+        <v>-7.9306821259999998</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H56" s="5">
-        <v>886</v>
+        <v>4795.3</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J56" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="K56" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="L56" s="18">
-        <v>17700</v>
-      </c>
-      <c r="M56" s="18">
-        <f>ABS((D56*E56)-L56)</f>
-        <v>300</v>
-      </c>
-      <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B56, $C$2:$C$706, C56, $D$2:$D$706, D56, $E$2:$E$706, E56) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="P56" s="24"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O56"/>
+      <c r="P56"/>
     </row>
     <row r="57" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="3">
-        <v>46283.375</v>
+      <c r="A57" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D57" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E57" s="4">
-        <v>870.2</v>
+        <v>18052</v>
       </c>
       <c r="F57" s="4">
-        <v>-1.7832957110000001</v>
+        <v>-7.9449260580000001</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H57" s="5">
-        <v>886</v>
+        <v>19610</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="K57" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="L57" s="18">
-        <v>17920</v>
-      </c>
-      <c r="M57" s="18">
-        <f>ABS((D57*E57)-L57)</f>
-        <v>516</v>
-      </c>
-      <c r="N57" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B57, $C$2:$C$706, C57, $D$2:$D$706, D57, $E$2:$E$706, E57) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
+      <c r="J57" s="50"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="58" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C58" s="1" t="s">
+      <c r="A58" s="54">
+        <v>46289.375</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="4">
-        <v>3</v>
-      </c>
-      <c r="E58" s="4">
-        <v>3810</v>
+      <c r="D58" s="5">
+        <v>5</v>
+      </c>
+      <c r="E58" s="5">
+        <v>601</v>
       </c>
       <c r="F58" s="4">
-        <v>-1.753481176</v>
+        <v>-7.9632465540000004</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="H58" s="5">
-        <v>3878</v>
+        <v>653</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="61"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B58, $C$2:$C$706, C58, $D$2:$D$706, D58, $E$2:$E$706, E58) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="J58" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K58" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="L58" s="18">
+        <v>3245</v>
+      </c>
+      <c r="M58" s="18">
+        <f>ABS((D58*E58)-L58)</f>
+        <v>240</v>
+      </c>
+      <c r="N58" s="10" t="str">
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O58" s="10"/>
       <c r="P58" s="10"/>
     </row>
     <row r="59" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="3">
-        <v>46287.375</v>
+      <c r="A59" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
@@ -4081,133 +4129,109 @@
         <v>1</v>
       </c>
       <c r="E59" s="4">
-        <v>19300</v>
+        <v>4164</v>
       </c>
       <c r="F59" s="4">
-        <v>-1.580826109</v>
+        <v>-8.6641807409999991</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="H59" s="5">
-        <v>19610</v>
+        <v>4559</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="K59" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="L59" s="18">
-        <v>19950</v>
-      </c>
-      <c r="M59" s="18">
-        <f>ABS((D59*E59)-L59)</f>
-        <v>650</v>
-      </c>
-      <c r="N59" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B59, $C$2:$C$706, C59, $D$2:$D$706, D59, $E$2:$E$706, E59) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
+      <c r="J59" s="50"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="60" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="4">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E60" s="4">
-        <v>201</v>
+        <v>1751</v>
       </c>
       <c r="F60" s="4">
-        <v>-1.5140379239999999</v>
+        <v>-10.112936339999999</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="H60" s="5">
-        <v>204.09</v>
+        <v>1948</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="64" t="s">
-        <v>41</v>
-      </c>
+      <c r="J60" s="50"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B60, $C$2:$C$706, C60, $D$2:$D$706, D60, $E$2:$E$706, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="61" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="3">
-        <v>46260.375</v>
+      <c r="A61" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D61" s="4">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="E61" s="4">
-        <v>2348</v>
+        <v>111</v>
       </c>
       <c r="F61" s="4">
-        <v>-1.327954278</v>
+        <v>-10.77170418</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H61" s="5">
-        <v>2379.6</v>
+        <v>124.4</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="K61" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="L61" s="18">
-        <v>7344</v>
-      </c>
-      <c r="M61" s="18">
-        <f>ABS((D61*E61)-L61)</f>
-        <v>300</v>
-      </c>
+      <c r="J61" s="50"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B61, $C$2:$C$706, C61, $D$2:$D$706, D61, $E$2:$E$706, E61) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="62" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="6" t="s">
-        <v>62</v>
+      <c r="A62" s="3">
+        <v>46287.375</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>49</v>
+        <v>291</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>10</v>
@@ -4216,26 +4240,35 @@
         <v>2</v>
       </c>
       <c r="E62" s="4">
-        <v>3830</v>
+        <v>1564</v>
       </c>
       <c r="F62" s="4">
-        <v>-1.237751418</v>
+        <v>-11.16160182</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>50</v>
+        <v>293</v>
       </c>
       <c r="H62" s="5">
-        <v>3878</v>
+        <v>1760.5</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="61"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B62, $C$2:$C$706, C62, $D$2:$D$706, D62, $E$2:$E$706, E62) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="J62" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="L62" s="18">
+        <v>3430</v>
+      </c>
+      <c r="M62" s="18">
+        <f>ABS((D62*E62)-L62)</f>
+        <v>302</v>
+      </c>
+      <c r="N62" s="10" t="str">
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="10"/>
@@ -4243,312 +4276,296 @@
     </row>
     <row r="63" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3">
-        <v>46252.6875</v>
+        <v>46288.479861111111</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D63" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E63" s="4">
-        <v>326</v>
+        <v>580</v>
       </c>
       <c r="F63" s="4">
-        <v>-1.212121212</v>
+        <v>-11.179173049999999</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H63" s="5">
-        <v>330</v>
+        <v>653</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J63" s="61" t="s">
+      <c r="J63" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B63, $C$2:$C$706, C63, $D$2:$D$706, D63, $E$2:$E$706, E63) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O63"/>
-      <c r="P63"/>
-    </row>
-    <row r="64" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="3">
-        <v>46252.635416666664</v>
+      <c r="K63" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="L63" s="18">
+        <v>3150</v>
+      </c>
+      <c r="M63" s="18">
+        <f>ABS((D63*E63)-L63)</f>
+        <v>250</v>
+      </c>
+      <c r="N63" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+    </row>
+    <row r="64" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D64" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" s="4">
-        <v>1302</v>
+        <v>4014</v>
       </c>
       <c r="F64" s="4">
-        <v>-1.138952164</v>
+        <v>-11.95437596</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="H64" s="5">
-        <v>1317</v>
+        <v>4559</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J64" s="61" t="s">
-        <v>41</v>
-      </c>
+      <c r="J64" s="50"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B64, $C$2:$C$706, C64, $D$2:$D$706, D64, $E$2:$E$706, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
       <c r="P64"/>
     </row>
-    <row r="65" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="3">
-        <v>46282.416666666664</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D65" s="4">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E65" s="4">
-        <v>880</v>
+        <v>2892</v>
       </c>
       <c r="F65" s="4">
-        <v>-0.89532068249999996</v>
+        <v>-12.852192260000001</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="H65" s="5">
-        <v>887.95</v>
+        <v>3318.5</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J65" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="K65" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="L65" s="18">
-        <v>35920</v>
-      </c>
-      <c r="M65" s="18">
-        <f>ABS((D65*E65)-L65)</f>
-        <v>720</v>
-      </c>
+      <c r="J65" s="50"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17"/>
+      <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B65, $C$2:$C$706, C65, $D$2:$D$706, D65, $E$2:$E$706, E65) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O65"/>
+      <c r="P65"/>
     </row>
     <row r="66" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D66" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4">
-        <v>3856</v>
+        <v>561</v>
       </c>
       <c r="F66" s="4">
-        <v>-0.56730273340000004</v>
+        <v>-14.08882083</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="H66" s="5">
-        <v>3878</v>
+        <v>653</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="61"/>
+      <c r="J66" s="50" t="s">
+        <v>41</v>
+      </c>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B66, $C$2:$C$706, C66, $D$2:$D$706, D66, $E$2:$E$706, E66) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O66" s="19"/>
-      <c r="P66" s="10"/>
+        <f t="shared" ref="N66:N97" si="2">IF(COUNTIFS( $B$2:$B$706, B66, $C$2:$C$706, C66, $D$2:$D$706, D66, $E$2:$E$706, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O66"/>
+      <c r="P66"/>
     </row>
     <row r="67" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="31">
-        <v>46288.375</v>
-      </c>
-      <c r="B67" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="32" t="s">
+      <c r="A67" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="33">
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>3914</v>
+      </c>
+      <c r="F67" s="4">
+        <v>-14.14783944</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H67" s="5">
+        <v>4559</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" t="str">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O67"/>
+      <c r="P67"/>
+    </row>
+    <row r="68" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E67" s="33">
-        <v>887</v>
-      </c>
-      <c r="F67" s="4">
-        <v>-0.1069880061</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H67" s="5">
-        <v>887.95</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J67" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="K67" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="L67" s="28">
-        <v>9170</v>
-      </c>
-      <c r="M67" s="28">
-        <f>ABS((D67*E67)-L67)</f>
-        <v>300</v>
-      </c>
-      <c r="N67" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B67, $C$2:$C$706, C67, $D$2:$D$706, D67, $E$2:$E$706, E67) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-    </row>
-    <row r="68" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="31">
-        <v>46288.375</v>
-      </c>
-      <c r="B68" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C68" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D68" s="33">
-        <v>10</v>
-      </c>
-      <c r="E68" s="33">
-        <v>887</v>
+      <c r="D68" s="4">
+        <v>4</v>
+      </c>
+      <c r="E68" s="4">
+        <v>701</v>
       </c>
       <c r="F68" s="4">
-        <v>-0.1069880061</v>
+        <v>-14.73056806</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="H68" s="5">
-        <v>887.95</v>
+        <v>822.1</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="K68" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="L68" s="28">
-        <v>9070</v>
-      </c>
-      <c r="M68" s="28">
-        <f>ABS((D68*E68)-L68)</f>
-        <v>200</v>
-      </c>
-      <c r="N68" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B68, $C$2:$C$706, C68, $D$2:$D$706, D68, $E$2:$E$706, E68) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-      <c r="O68" s="30"/>
-      <c r="P68" s="30"/>
+      <c r="J68" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
+      <c r="M68" s="17"/>
+      <c r="N68" t="str">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O68"/>
+      <c r="P68"/>
     </row>
     <row r="69" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="3">
-        <v>46261.375</v>
+        <v>46281.416666666664</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>23</v>
+        <v>282</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D69" s="4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4">
-        <v>204</v>
+        <v>726</v>
       </c>
       <c r="F69" s="4">
-        <v>-4.4098191969999999E-2</v>
+        <v>-16.108158079999999</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>70</v>
+        <v>289</v>
       </c>
       <c r="H69" s="5">
-        <v>204.09</v>
+        <v>865.4</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="60" t="s">
+      <c r="J69" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K69" s="18" t="s">
-        <v>185</v>
+        <v>284</v>
       </c>
       <c r="L69" s="18">
-        <v>10550</v>
+        <v>17940</v>
       </c>
       <c r="M69" s="18">
         <f>ABS((D69*E69)-L69)</f>
-        <v>350</v>
+        <v>10680</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B69, $C$2:$C$706, C69, $D$2:$D$706, D69, $E$2:$E$706, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4557,40 +4574,43 @@
         <v>62</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D70" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E70" s="4">
-        <v>3888</v>
+        <v>2752</v>
       </c>
       <c r="F70" s="4">
-        <v>0.25786487879999997</v>
+        <v>-17.0709658</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H70" s="5">
-        <v>3878</v>
+        <v>3318.5</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J70" s="61"/>
+      <c r="J70" s="50" t="s">
+        <v>41</v>
+      </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B70, $C$2:$C$706, C70, $D$2:$D$706, D70, $E$2:$E$706, E70) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O70" s="25"/>
-    </row>
-    <row r="71" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O70"/>
+      <c r="P70"/>
+    </row>
+    <row r="71" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3">
         <v>46268.375</v>
       </c>
@@ -4632,59 +4652,55 @@
         <v>1200</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B71, $C$2:$C$706, C71, $D$2:$D$706, D71, $E$2:$E$706, E71) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="3">
-        <v>46275.457638888889</v>
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O71" s="39" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D72" s="4">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E72" s="4">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="F72" s="4">
-        <v>1.3976431899999999</v>
+        <v>-18.128654969999999</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="H72" s="5">
-        <v>218.94</v>
+        <v>239.4</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="60" t="s">
+      <c r="J72" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="K72" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="L72" s="18">
-        <v>56375</v>
-      </c>
-      <c r="M72" s="18">
-        <f>ABS((D72*E72)-L72)</f>
-        <v>34175</v>
-      </c>
-      <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B72, $C$2:$C$706, C72, $D$2:$D$706, D72, $E$2:$E$706, E72) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O72" s="10"/>
-      <c r="P72" s="10"/>
-    </row>
-    <row r="73" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
+      <c r="M72" s="17"/>
+      <c r="N72" t="str">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O72"/>
+      <c r="P72"/>
+    </row>
+    <row r="73" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3">
         <v>46276.375</v>
       </c>
@@ -4726,20 +4742,18 @@
         <v>646</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B73, $C$2:$C$706, C73, $D$2:$D$706, D73, $E$2:$E$706, E73) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O73" s="39" t="s">
-        <v>242</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O73" s="67"/>
       <c r="P73" s="10"/>
     </row>
-    <row r="74" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
-        <v>46252.645138888889</v>
+        <v>46281.416666666664</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>68</v>
+        <v>282</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>10</v>
@@ -4748,70 +4762,78 @@
         <v>10</v>
       </c>
       <c r="E74" s="4">
-        <v>401</v>
+        <v>706</v>
       </c>
       <c r="F74" s="4">
-        <v>2.1135727019999999</v>
+        <v>-18.419228100000002</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>69</v>
+        <v>289</v>
       </c>
       <c r="H74" s="5">
-        <v>392.7</v>
+        <v>865.4</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J74" s="62" t="s">
+      <c r="J74" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K74" s="17"/>
-      <c r="L74" s="17"/>
-      <c r="M74" s="17"/>
-      <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B74, $C$2:$C$706, C74, $D$2:$D$706, D74, $E$2:$E$706, E74) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="6" t="s">
-        <v>62</v>
+      <c r="K74" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="L74" s="18">
+        <v>17940</v>
+      </c>
+      <c r="M74" s="18">
+        <f>ABS((D74*E74)-L74)</f>
+        <v>10880</v>
+      </c>
+      <c r="N74" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="3">
+        <v>46252.688194444447</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D75" s="4">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E75" s="4">
-        <v>281</v>
+        <v>136.15</v>
       </c>
       <c r="F75" s="4">
-        <v>2.2934109939999998</v>
+        <v>-19.46646161</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H75" s="5">
-        <v>274.7</v>
+        <v>169.06</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J75" s="61" t="s">
-        <v>41</v>
+      <c r="J75" s="50" t="s">
+        <v>55</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B75, $C$2:$C$706, C75, $D$2:$D$706, D75, $E$2:$E$706, E75) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="P75" s="25"/>
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O75"/>
+      <c r="P75"/>
     </row>
     <row r="76" spans="1:16" s="24" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3">
@@ -4851,11 +4873,11 @@
         <v>32900</v>
       </c>
       <c r="M76" s="18">
-        <f>ABS((D76*E76)-L76)</f>
+        <f t="shared" ref="M76:M91" si="3">ABS((D76*E76)-L76)</f>
         <v>1000</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B76, $C$2:$C$706, C76, $D$2:$D$706, D76, $E$2:$E$706, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="10"/>
@@ -4899,11 +4921,11 @@
         <v>11660</v>
       </c>
       <c r="M77" s="18">
-        <f>ABS((D77*E77)-L77)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B77, $C$2:$C$706, C77, $D$2:$D$706, D77, $E$2:$E$706, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="39" t="s">
@@ -4948,11 +4970,11 @@
         <v>4640</v>
       </c>
       <c r="M78" s="18">
-        <f>ABS((D78*E78)-L78)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B78, $C$2:$C$706, C78, $D$2:$D$706, D78, $E$2:$E$706, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="39" t="s">
@@ -4997,11 +5019,11 @@
         <v>15300</v>
       </c>
       <c r="M79" s="18">
-        <f>ABS((D79*E79)-L79)</f>
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B79, $C$2:$C$706, C79, $D$2:$D$706, D79, $E$2:$E$706, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5043,11 +5065,11 @@
         <v>16755</v>
       </c>
       <c r="M80" s="18">
-        <f>ABS((D80*E80)-L80)</f>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B80, $C$2:$C$706, C80, $D$2:$D$706, D80, $E$2:$E$706, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5089,11 +5111,11 @@
         <v>10250</v>
       </c>
       <c r="M81" s="18">
-        <f>ABS((D81*E81)-L81)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B81, $C$2:$C$706, C81, $D$2:$D$706, D81, $E$2:$E$706, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="10"/>
@@ -5137,11 +5159,11 @@
         <v>8220</v>
       </c>
       <c r="M82" s="18">
-        <f>ABS((D82*E82)-L82)</f>
+        <f t="shared" si="3"/>
         <v>360</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B82, $C$2:$C$706, C82, $D$2:$D$706, D82, $E$2:$E$706, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O82" s="39" t="s">
@@ -5187,11 +5209,11 @@
         <v>3160</v>
       </c>
       <c r="M83" s="18">
-        <f>ABS((D83*E83)-L83)</f>
+        <f t="shared" si="3"/>
         <v>235</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B83, $C$2:$C$706, C83, $D$2:$D$706, D83, $E$2:$E$706, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5233,11 +5255,11 @@
         <v>5585</v>
       </c>
       <c r="M84" s="28">
-        <f>ABS((D84*E84)-L84)</f>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="N84" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B84, $C$2:$C$706, C84, $D$2:$D$706, D84, $E$2:$E$706, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O84" s="39" t="s">
@@ -5283,11 +5305,11 @@
         <v>5730</v>
       </c>
       <c r="M85" s="28">
-        <f>ABS((D85*E85)-L85)</f>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="N85" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B85, $C$2:$C$706, C85, $D$2:$D$706, D85, $E$2:$E$706, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O85" s="39" t="s">
@@ -5333,11 +5355,11 @@
         <v>39300</v>
       </c>
       <c r="M86" s="18">
-        <f>ABS((D86*E86)-L86)</f>
+        <f t="shared" si="3"/>
         <v>18850</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B86, $C$2:$C$706, C86, $D$2:$D$706, D86, $E$2:$E$706, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5379,11 +5401,11 @@
         <v>33200</v>
       </c>
       <c r="M87" s="18">
-        <f>ABS((D87*E87)-L87)</f>
+        <f t="shared" si="3"/>
         <v>1200</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B87, $C$2:$C$706, C87, $D$2:$D$706, D87, $E$2:$E$706, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5425,11 +5447,11 @@
         <v>19730.5</v>
       </c>
       <c r="M88" s="28">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" si="3"/>
         <v>504.5</v>
       </c>
       <c r="N88" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B88, $C$2:$C$706, C88, $D$2:$D$706, D88, $E$2:$E$706, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O88" s="39" t="s">
@@ -5474,11 +5496,11 @@
         <v>19690</v>
       </c>
       <c r="M89" s="28">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="3"/>
         <v>545</v>
       </c>
       <c r="N89" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B89, $C$2:$C$706, C89, $D$2:$D$706, D89, $E$2:$E$706, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O89" s="39" t="s">
@@ -5524,11 +5546,11 @@
         <v>8970</v>
       </c>
       <c r="M90" s="18">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B90, $C$2:$C$706, C90, $D$2:$D$706, D90, $E$2:$E$706, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5570,57 +5592,55 @@
         <v>6367.2</v>
       </c>
       <c r="M91" s="18">
-        <f>ABS((D91*E91)-L91)</f>
+        <f t="shared" si="3"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B91, $C$2:$C$706, C91, $D$2:$D$706, D91, $E$2:$E$706, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="3">
-        <v>46031.4375</v>
+    <row r="92" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D92" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92" s="4">
-        <v>1052</v>
+        <v>2660</v>
       </c>
       <c r="F92" s="4">
-        <v>4.6766169150000003</v>
+        <v>-19.843302699999999</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>221</v>
+        <v>93</v>
       </c>
       <c r="H92" s="5">
-        <v>1005</v>
+        <v>3318.5</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J92" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="M92" s="18">
-        <f>ABS((D92*E92)-L92)</f>
-        <v>3156</v>
-      </c>
-      <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B92, $C$2:$C$706, C92, $D$2:$D$706, D92, $E$2:$E$706, E92) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="P92" s="19"/>
+      <c r="J92" s="50"/>
+      <c r="K92" s="17"/>
+      <c r="L92" s="17"/>
+      <c r="M92" s="17"/>
+      <c r="N92" t="str">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O92"/>
+      <c r="P92"/>
     </row>
     <row r="93" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3">
@@ -5664,7 +5684,7 @@
         <v>300</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B93, $C$2:$C$706, C93, $D$2:$D$706, D93, $E$2:$E$706, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5710,7 +5730,7 @@
         <v>275</v>
       </c>
       <c r="N94" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B94, $C$2:$C$706, C94, $D$2:$D$706, D94, $E$2:$E$706, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -5756,7 +5776,7 @@
         <v>225</v>
       </c>
       <c r="N95" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B95, $C$2:$C$706, C95, $D$2:$D$706, D95, $E$2:$E$706, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -5765,39 +5785,41 @@
         <v>62</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D96" s="4">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E96" s="4">
-        <v>2435</v>
+        <v>2560</v>
       </c>
       <c r="F96" s="4">
-        <v>5.1472493310000003</v>
+        <v>-22.85671237</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H96" s="5">
-        <v>2315.8000000000002</v>
+        <v>3318.5</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="61" t="s">
-        <v>55</v>
+      <c r="J96" s="50" t="s">
+        <v>41</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B96, $C$2:$C$706, C96, $D$2:$D$706, D96, $E$2:$E$706, E96) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+      <c r="O96"/>
+      <c r="P96"/>
     </row>
     <row r="97" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3">
@@ -5837,57 +5859,57 @@
         <v>8400</v>
       </c>
       <c r="M97" s="18">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" ref="M97:M110" si="4">ABS((D97*E97)-L97)</f>
         <v>300</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B97, $C$2:$C$706, C97, $D$2:$D$706, D97, $E$2:$E$706, E97) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="3">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="61">
         <v>46266.642361111109</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" s="4">
+      <c r="C98" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="63">
         <v>100</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E98" s="63">
         <v>348</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="63">
         <v>5.4545454549999999</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="H98" s="5">
+      <c r="H98" s="65">
         <v>330</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J98" s="18" t="s">
+      <c r="I98" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J98" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="K98" s="18" t="s">
+      <c r="K98" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="L98" s="18">
+      <c r="L98" s="66">
         <v>33950</v>
       </c>
-      <c r="M98" s="18">
-        <f>ABS((D98*E98)-L98)</f>
+      <c r="M98" s="66">
+        <f t="shared" si="4"/>
         <v>850</v>
       </c>
-      <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B98, $C$2:$C$706, C98, $D$2:$D$706, D98, $E$2:$E$706, E98) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="N98" s="25" t="str">
+        <f t="shared" ref="N98:N115" si="5">IF(COUNTIFS( $B$2:$B$706, B98, $C$2:$C$706, C98, $D$2:$D$706, D98, $E$2:$E$706, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -5929,11 +5951,11 @@
         <v>20010</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B99, $C$2:$C$706, C99, $D$2:$D$706, D99, $E$2:$E$706, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P99"/>
@@ -5976,11 +5998,11 @@
         <v>9170</v>
       </c>
       <c r="M100" s="28">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B100, $C$2:$C$706, C100, $D$2:$D$706, D100, $E$2:$E$706, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="39" t="s">
@@ -6026,11 +6048,11 @@
         <v>8420</v>
       </c>
       <c r="M101" s="18">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B101, $C$2:$C$706, C101, $D$2:$D$706, D101, $E$2:$E$706, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6072,11 +6094,11 @@
         <v>9886</v>
       </c>
       <c r="M102" s="18">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="4"/>
         <v>654</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B102, $C$2:$C$706, C102, $D$2:$D$706, D102, $E$2:$E$706, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6118,11 +6140,11 @@
         <v>17150</v>
       </c>
       <c r="M103" s="18">
-        <f>ABS((D103*E103)-L103)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B103, $C$2:$C$706, C103, $D$2:$D$706, D103, $E$2:$E$706, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6164,11 +6186,11 @@
         <v>4200</v>
       </c>
       <c r="M104" s="18">
-        <f>ABS((D104*E104)-L104)</f>
+        <f t="shared" si="4"/>
         <v>290</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B104, $C$2:$C$706, C104, $D$2:$D$706, D104, $E$2:$E$706, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6210,11 +6232,11 @@
         <v>14100</v>
       </c>
       <c r="M105" s="18">
-        <f>ABS((D105*E105)-L105)</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B105, $C$2:$C$706, C105, $D$2:$D$706, D105, $E$2:$E$706, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="10"/>
@@ -6258,11 +6280,11 @@
         <v>20260</v>
       </c>
       <c r="M106" s="18">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N106" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B106, $C$2:$C$706, C106, $D$2:$D$706, D106, $E$2:$E$706, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O106"/>
@@ -6306,11 +6328,11 @@
         <v>4120</v>
       </c>
       <c r="M107" s="28">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="N107" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B107, $C$2:$C$706, C107, $D$2:$D$706, D107, $E$2:$E$706, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="40" t="s">
@@ -6356,11 +6378,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M108" s="28">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" si="4"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N108" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B108, $C$2:$C$706, C108, $D$2:$D$706, D108, $E$2:$E$706, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O108" s="40" t="s">
@@ -6396,7 +6418,7 @@
       <c r="I109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J109" s="60" t="s">
+      <c r="J109" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K109" s="18" t="s">
@@ -6406,11 +6428,11 @@
         <v>16500</v>
       </c>
       <c r="M109" s="18">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="4"/>
         <v>1400</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B109, $C$2:$C$706, C109, $D$2:$D$706, D109, $E$2:$E$706, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="39" t="s">
@@ -6455,11 +6477,11 @@
         <v>3300</v>
       </c>
       <c r="M110" s="18">
-        <f>ABS((D110*E110)-L110)</f>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B110, $C$2:$C$706, C110, $D$2:$D$706, D110, $E$2:$E$706, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6493,7 +6515,7 @@
       </c>
       <c r="J111" s="35"/>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B111, $C$2:$C$706, C111, $D$2:$D$706, D111, $E$2:$E$706, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6529,7 +6551,7 @@
         <v>118</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B112, $C$2:$C$706, C112, $D$2:$D$706, D112, $E$2:$E$706, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6575,7 +6597,7 @@
         <v>496</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B113, $C$2:$C$706, C113, $D$2:$D$706, D113, $E$2:$E$706, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6621,49 +6643,50 @@
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B114, $C$2:$C$706, C114, $D$2:$D$706, D114, $E$2:$E$706, E114) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D115" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E115" s="4">
-        <v>2470</v>
+        <v>660</v>
       </c>
       <c r="F115" s="4">
-        <v>6.6586060969999998</v>
+        <v>-29.943742700000001</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="H115" s="5">
-        <v>2315.8000000000002</v>
+        <v>942.1</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J115" s="61" t="s">
+      <c r="J115" s="50" t="s">
         <v>41</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B115, $C$2:$C$706, C115, $D$2:$D$706, D115, $E$2:$E$706, E115) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="P115" s="24"/>
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+      <c r="O115"/>
+      <c r="P115"/>
     </row>
     <row r="116" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
@@ -6707,7 +6730,7 @@
         <v>18350</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B116, $C$2:$C$706, C116, $D$2:$D$706, D116, $E$2:$E$706, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N116:N129" si="6">IF(COUNTIFS( $B$2:$B$706, B116, $C$2:$C$706, C116, $D$2:$D$706, D116, $E$2:$E$706, E116) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -6753,7 +6776,7 @@
         <v>645</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B117, $C$2:$C$706, C117, $D$2:$D$706, D117, $E$2:$E$706, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="39" t="s">
@@ -6802,7 +6825,7 @@
         <v>500</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B118, $C$2:$C$706, C118, $D$2:$D$706, D118, $E$2:$E$706, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="10"/>
@@ -6845,7 +6868,7 @@
       <c r="L119" s="18"/>
       <c r="M119" s="18"/>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B119, $C$2:$C$706, C119, $D$2:$D$706, D119, $E$2:$E$706, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="10"/>
@@ -6893,7 +6916,7 @@
         <v>4451</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B120, $C$2:$C$706, C120, $D$2:$D$706, D120, $E$2:$E$706, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="39" t="s">
@@ -6942,7 +6965,7 @@
         <v>250</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B121, $C$2:$C$706, C121, $D$2:$D$706, D121, $E$2:$E$706, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6988,7 +7011,7 @@
         <v>280</v>
       </c>
       <c r="N122" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B122, $C$2:$C$706, C122, $D$2:$D$706, D122, $E$2:$E$706, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="39" t="s">
@@ -7025,7 +7048,7 @@
       </c>
       <c r="J123" s="35"/>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B123, $C$2:$C$706, C123, $D$2:$D$706, D123, $E$2:$E$706, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7071,7 +7094,7 @@
         <v>300</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B124, $C$2:$C$706, C124, $D$2:$D$706, D124, $E$2:$E$706, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7117,7 +7140,7 @@
         <v>275</v>
       </c>
       <c r="N125" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B125, $C$2:$C$706, C125, $D$2:$D$706, D125, $E$2:$E$706, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7151,7 +7174,7 @@
       </c>
       <c r="J126" s="35"/>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B126, $C$2:$C$706, C126, $D$2:$D$706, D126, $E$2:$E$706, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="24"/>
@@ -7198,7 +7221,7 @@
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B127, $C$2:$C$706, C127, $D$2:$D$706, D127, $E$2:$E$706, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P127" s="19"/>
@@ -7245,7 +7268,7 @@
         <v>300</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B128, $C$2:$C$706, C128, $D$2:$D$706, D128, $E$2:$E$706, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P128" s="30"/>
@@ -7280,7 +7303,7 @@
       </c>
       <c r="J129" s="35"/>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B129, $C$2:$C$706, C129, $D$2:$D$706, D129, $E$2:$E$706, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="39" t="s">
@@ -7330,7 +7353,7 @@
         <v>320</v>
       </c>
       <c r="N130" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B130, $C$2:$C$706, C130, $D$2:$D$706, D130, $E$2:$E$706, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="7">IF(COUNTIFS( $B$2:$B$706, B130, $C$2:$C$706, C130, $D$2:$D$706, D130, $E$2:$E$706, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="30"/>
@@ -7378,7 +7401,7 @@
         <v>235</v>
       </c>
       <c r="N131" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B131, $C$2:$C$706, C131, $D$2:$D$706, D131, $E$2:$E$706, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7412,7 +7435,7 @@
       </c>
       <c r="J132" s="35"/>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B132, $C$2:$C$706, C132, $D$2:$D$706, D132, $E$2:$E$706, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="30"/>
@@ -7455,11 +7478,11 @@
         <v>14400</v>
       </c>
       <c r="M133" s="18">
-        <f>ABS((D133*E133)-L133)</f>
+        <f t="shared" ref="M133:M140" si="8">ABS((D133*E133)-L133)</f>
         <v>500</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B133, $C$2:$C$706, C133, $D$2:$D$706, D133, $E$2:$E$706, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7501,11 +7524,11 @@
         <v>4852</v>
       </c>
       <c r="M134" s="18">
-        <f>ABS((D134*E134)-L134)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B134, $C$2:$C$706, C134, $D$2:$D$706, D134, $E$2:$E$706, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7547,11 +7570,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M135" s="18">
-        <f>ABS((D135*E135)-L135)</f>
+        <f t="shared" si="8"/>
         <v>710.99999999999636</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B135, $C$2:$C$706, C135, $D$2:$D$706, D135, $E$2:$E$706, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P135"/>
@@ -7594,11 +7617,11 @@
         <v>34100</v>
       </c>
       <c r="M136" s="18">
-        <f>ABS((D136*E136)-L136)</f>
+        <f t="shared" si="8"/>
         <v>1700</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B136, $C$2:$C$706, C136, $D$2:$D$706, D136, $E$2:$E$706, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P136" s="10"/>
@@ -7641,11 +7664,11 @@
         <v>14130</v>
       </c>
       <c r="M137" s="18">
-        <f>ABS((D137*E137)-L137)</f>
+        <f t="shared" si="8"/>
         <v>714</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B137, $C$2:$C$706, C137, $D$2:$D$706, D137, $E$2:$E$706, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7687,11 +7710,11 @@
         <v>8570</v>
       </c>
       <c r="M138" s="28">
-        <f>ABS((D138*E138)-L138)</f>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B138, $C$2:$C$706, C138, $D$2:$D$706, D138, $E$2:$E$706, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="39" t="s">
@@ -7736,11 +7759,11 @@
         <v>6105</v>
       </c>
       <c r="M139" s="28">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
       <c r="N139" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B139, $C$2:$C$706, C139, $D$2:$D$706, D139, $E$2:$E$706, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -7782,11 +7805,11 @@
         <v>6005</v>
       </c>
       <c r="M140" s="28">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N140" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B140, $C$2:$C$706, C140, $D$2:$D$706, D140, $E$2:$E$706, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -7825,7 +7848,7 @@
       <c r="L141" s="18"/>
       <c r="M141" s="18"/>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B141, $C$2:$C$706, C141, $D$2:$D$706, D141, $E$2:$E$706, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="10"/>
@@ -7863,7 +7886,7 @@
         <v>117</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B142, $C$2:$C$706, C142, $D$2:$D$706, D142, $E$2:$E$706, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7909,7 +7932,7 @@
         <v>300</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B143, $C$2:$C$706, C143, $D$2:$D$706, D143, $E$2:$E$706, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="30"/>
@@ -7956,7 +7979,7 @@
         <v>300</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B144, $C$2:$C$706, C144, $D$2:$D$706, D144, $E$2:$E$706, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="10"/>
@@ -8004,7 +8027,7 @@
         <v>250</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B145, $C$2:$C$706, C145, $D$2:$D$706, D145, $E$2:$E$706, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8050,7 +8073,7 @@
         <v>500</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B146, $C$2:$C$706, C146, $D$2:$D$706, D146, $E$2:$E$706, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="40" t="s">
@@ -8089,7 +8112,7 @@
         <v>118</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B147, $C$2:$C$706, C147, $D$2:$D$706, D147, $E$2:$E$706, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P147"/>
@@ -8136,7 +8159,7 @@
         <v>501</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B148, $C$2:$C$706, C148, $D$2:$D$706, D148, $E$2:$E$706, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="39" t="s">
@@ -8176,7 +8199,7 @@
       <c r="L149" s="18"/>
       <c r="M149" s="18"/>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B149, $C$2:$C$706, C149, $D$2:$D$706, D149, $E$2:$E$706, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="10"/>
@@ -8220,11 +8243,11 @@
         <v>16580</v>
       </c>
       <c r="M150" s="45">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" ref="M150:M157" si="9">ABS((D150*E150)-L150)</f>
         <v>660</v>
       </c>
       <c r="N150" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B150, $C$2:$C$706, C150, $D$2:$D$706, D150, $E$2:$E$706, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="24"/>
@@ -8270,11 +8293,11 @@
         <v>14650</v>
       </c>
       <c r="M151" s="18">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="9"/>
         <v>450</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B151, $C$2:$C$706, C151, $D$2:$D$706, D151, $E$2:$E$706, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8316,11 +8339,11 @@
         <v>73800</v>
       </c>
       <c r="M152" s="18">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" si="9"/>
         <v>48320</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B152, $C$2:$C$706, C152, $D$2:$D$706, D152, $E$2:$E$706, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="39" t="s">
@@ -8365,11 +8388,11 @@
         <v>9470</v>
       </c>
       <c r="M153" s="18">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B153, $C$2:$C$706, C153, $D$2:$D$706, D153, $E$2:$E$706, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8411,11 +8434,11 @@
         <v>4680</v>
       </c>
       <c r="M154" s="28">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="9"/>
         <v>140</v>
       </c>
       <c r="N154" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B154, $C$2:$C$706, C154, $D$2:$D$706, D154, $E$2:$E$706, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="P154" s="30"/>
@@ -8458,11 +8481,11 @@
         <v>4520</v>
       </c>
       <c r="M155" s="28">
-        <f>ABS((D155*E155)-L155)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N155" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B155, $C$2:$C$706, C155, $D$2:$D$706, D155, $E$2:$E$706, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8504,11 +8527,11 @@
         <v>10510</v>
       </c>
       <c r="M156" s="18">
-        <f>ABS((D156*E156)-L156)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B156, $C$2:$C$706, C156, $D$2:$D$706, D156, $E$2:$E$706, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8550,11 +8573,11 @@
         <v>3810</v>
       </c>
       <c r="M157" s="18">
-        <f>ABS((D157*E157)-L157)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N157" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B157, $C$2:$C$706, C157, $D$2:$D$706, D157, $E$2:$E$706, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8588,7 +8611,7 @@
       </c>
       <c r="J158" s="35"/>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B158, $C$2:$C$706, C158, $D$2:$D$706, D158, $E$2:$E$706, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8622,7 +8645,7 @@
       </c>
       <c r="J159" s="35"/>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B159, $C$2:$C$706, C159, $D$2:$D$706, D159, $E$2:$E$706, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8668,7 +8691,7 @@
         <v>294</v>
       </c>
       <c r="N160" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B160, $C$2:$C$706, C160, $D$2:$D$706, D160, $E$2:$E$706, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O160" s="10"/>
@@ -8716,7 +8739,7 @@
         <v>294</v>
       </c>
       <c r="N161" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B161, $C$2:$C$706, C161, $D$2:$D$706, D161, $E$2:$E$706, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O161" s="10"/>
@@ -8764,7 +8787,7 @@
         <v>280</v>
       </c>
       <c r="N162" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B162, $C$2:$C$706, C162, $D$2:$D$706, D162, $E$2:$E$706, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O162" s="30"/>
@@ -8802,7 +8825,7 @@
         <v>118</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B163, $C$2:$C$706, C163, $D$2:$D$706, D163, $E$2:$E$706, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8848,7 +8871,7 @@
         <v>300</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B164, $C$2:$C$706, C164, $D$2:$D$706, D164, $E$2:$E$706, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O164"/>
@@ -8895,7 +8918,7 @@
         <v>300</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B165, $C$2:$C$706, C165, $D$2:$D$706, D165, $E$2:$E$706, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O165" s="39" t="s">
@@ -8945,7 +8968,7 @@
         <v>650</v>
       </c>
       <c r="N166" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B166, $C$2:$C$706, C166, $D$2:$D$706, D166, $E$2:$E$706, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8979,7 +9002,7 @@
       </c>
       <c r="J167" s="35"/>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B167, $C$2:$C$706, C167, $D$2:$D$706, D167, $E$2:$E$706, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9025,7 +9048,7 @@
         <v>300</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B168, $C$2:$C$706, C168, $D$2:$D$706, D168, $E$2:$E$706, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9071,7 +9094,7 @@
         <v>300</v>
       </c>
       <c r="N169" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B169, $C$2:$C$706, C169, $D$2:$D$706, D169, $E$2:$E$706, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="30"/>
@@ -9119,7 +9142,7 @@
         <v>188</v>
       </c>
       <c r="N170" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B170, $C$2:$C$706, C170, $D$2:$D$706, D170, $E$2:$E$706, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="30"/>
@@ -9157,7 +9180,7 @@
         <v>118</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B171, $C$2:$C$706, C171, $D$2:$D$706, D171, $E$2:$E$706, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9199,11 +9222,11 @@
         <v>2105</v>
       </c>
       <c r="M172" s="26">
-        <f>ABS((D172*E172)-L172)</f>
+        <f t="shared" ref="M172:M178" si="10">ABS((D172*E172)-L172)</f>
         <v>250</v>
       </c>
       <c r="N172" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B172, $C$2:$C$706, C172, $D$2:$D$706, D172, $E$2:$E$706, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O172" s="10"/>
@@ -9247,11 +9270,11 @@
         <v>5520</v>
       </c>
       <c r="M173" s="28">
-        <f>ABS((D173*E173)-L173)</f>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
       <c r="N173" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B173, $C$2:$C$706, C173, $D$2:$D$706, D173, $E$2:$E$706, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="39" t="s">
@@ -9296,11 +9319,11 @@
         <v>2657</v>
       </c>
       <c r="M174" s="28">
-        <f>ABS((D174*E174)-L174)</f>
+        <f t="shared" si="10"/>
         <v>253</v>
       </c>
       <c r="N174" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B174, $C$2:$C$706, C174, $D$2:$D$706, D174, $E$2:$E$706, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O174" s="39" t="s">
@@ -9345,11 +9368,11 @@
         <v>2554.5</v>
       </c>
       <c r="M175" s="28">
-        <f>ABS((D175*E175)-L175)</f>
+        <f t="shared" si="10"/>
         <v>355.5</v>
       </c>
       <c r="N175" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B175, $C$2:$C$706, C175, $D$2:$D$706, D175, $E$2:$E$706, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O175" s="39" t="s">
@@ -9395,11 +9418,11 @@
         <v>20070</v>
       </c>
       <c r="M176" s="18">
-        <f>ABS((D176*E176)-L176)</f>
+        <f t="shared" si="10"/>
         <v>810</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B176, $C$2:$C$706, C176, $D$2:$D$706, D176, $E$2:$E$706, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9441,11 +9464,11 @@
         <v>8820</v>
       </c>
       <c r="M177" s="28">
-        <f>ABS((D177*E177)-L177)</f>
+        <f t="shared" si="10"/>
         <v>650</v>
       </c>
       <c r="N177" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B177, $C$2:$C$706, C177, $D$2:$D$706, D177, $E$2:$E$706, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9487,11 +9510,11 @@
         <v>36946</v>
       </c>
       <c r="M178" s="28">
-        <f>ABS((D178*E178)-L178)</f>
+        <f t="shared" si="10"/>
         <v>934</v>
       </c>
       <c r="N178" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B178, $C$2:$C$706, C178, $D$2:$D$706, D178, $E$2:$E$706, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O178" s="30"/>
@@ -9527,7 +9550,7 @@
       </c>
       <c r="J179" s="35"/>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B179, $C$2:$C$706, C179, $D$2:$D$706, D179, $E$2:$E$706, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P179" s="30"/>
@@ -9574,7 +9597,7 @@
         <v>47900</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B180, $C$2:$C$706, C180, $D$2:$D$706, D180, $E$2:$E$706, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="39" t="s">
@@ -9613,7 +9636,7 @@
         <v>118</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B181, $C$2:$C$706, C181, $D$2:$D$706, D181, $E$2:$E$706, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="39" t="s">
@@ -9652,7 +9675,7 @@
         <v>195</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B182, $C$2:$C$706, C182, $D$2:$D$706, D182, $E$2:$E$706, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9698,7 +9721,7 @@
         <v>880</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B183, $C$2:$C$706, C183, $D$2:$D$706, D183, $E$2:$E$706, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="39" t="s">
@@ -9747,7 +9770,7 @@
         <v>800</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B184, $C$2:$C$706, C184, $D$2:$D$706, D184, $E$2:$E$706, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="39" t="s">
@@ -9796,7 +9819,7 @@
         <v>650</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B185, $C$2:$C$706, C185, $D$2:$D$706, D185, $E$2:$E$706, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="39" t="s">
@@ -9845,7 +9868,7 @@
         <v>495</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B186, $C$2:$C$706, C186, $D$2:$D$706, D186, $E$2:$E$706, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O186" s="39" t="s">
@@ -9884,7 +9907,7 @@
         <v>117</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B187, $C$2:$C$706, C187, $D$2:$D$706, D187, $E$2:$E$706, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9930,7 +9953,7 @@
         <v>650</v>
       </c>
       <c r="N188" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B188, $C$2:$C$706, C188, $D$2:$D$706, D188, $E$2:$E$706, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P188" s="30"/>
@@ -9970,7 +9993,7 @@
       <c r="L189" s="45"/>
       <c r="M189" s="45"/>
       <c r="N189" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B189, $C$2:$C$706, C189, $D$2:$D$706, D189, $E$2:$E$706, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O189" s="24"/>
@@ -10020,7 +10043,7 @@
         <v>290</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B190, $C$2:$C$706, C190, $D$2:$D$706, D190, $E$2:$E$706, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10056,7 +10079,7 @@
         <v>117</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B191, $C$2:$C$706, C191, $D$2:$D$706, D191, $E$2:$E$706, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10102,7 +10125,7 @@
         <v>450</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B192, $C$2:$C$706, C192, $D$2:$D$706, D192, $E$2:$E$706, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10148,7 +10171,7 @@
         <v>527.5</v>
       </c>
       <c r="N193" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B193, $C$2:$C$706, C193, $D$2:$D$706, D193, $E$2:$E$706, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="30"/>
@@ -10191,7 +10214,7 @@
       <c r="L194" s="28"/>
       <c r="M194" s="28"/>
       <c r="N194" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B194, $C$2:$C$706, C194, $D$2:$D$706, D194, $E$2:$E$706, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="11">IF(COUNTIFS( $B$2:$B$706, B194, $C$2:$C$706, C194, $D$2:$D$706, D194, $E$2:$E$706, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O194" s="30"/>
@@ -10229,7 +10252,7 @@
         <v>117</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B195, $C$2:$C$706, C195, $D$2:$D$706, D195, $E$2:$E$706, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10275,7 +10298,7 @@
         <v>300</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B196, $C$2:$C$706, C196, $D$2:$D$706, D196, $E$2:$E$706, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O196" s="10"/>
@@ -10323,7 +10346,7 @@
         <v>816</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B197, $C$2:$C$706, C197, $D$2:$D$706, D197, $E$2:$E$706, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10359,7 +10382,7 @@
         <v>117</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B198, $C$2:$C$706, C198, $D$2:$D$706, D198, $E$2:$E$706, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10405,7 +10428,7 @@
         <v>300</v>
       </c>
       <c r="N199" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B199, $C$2:$C$706, C199, $D$2:$D$706, D199, $E$2:$E$706, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="39" t="s">
@@ -10443,7 +10466,7 @@
       </c>
       <c r="J200" s="35"/>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B200, $C$2:$C$706, C200, $D$2:$D$706, D200, $E$2:$E$706, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10479,7 +10502,7 @@
         <v>118</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B201, $C$2:$C$706, C201, $D$2:$D$706, D201, $E$2:$E$706, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O201" s="30"/>
@@ -10526,7 +10549,7 @@
         <v>650</v>
       </c>
       <c r="N202" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B202, $C$2:$C$706, C202, $D$2:$D$706, D202, $E$2:$E$706, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O202"/>
@@ -10574,7 +10597,7 @@
         <v>250</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B203, $C$2:$C$706, C203, $D$2:$D$706, D203, $E$2:$E$706, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10620,7 +10643,7 @@
         <v>300</v>
       </c>
       <c r="N204" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B204, $C$2:$C$706, C204, $D$2:$D$706, D204, $E$2:$E$706, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10666,7 +10689,7 @@
         <v>260</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B205, $C$2:$C$706, C205, $D$2:$D$706, D205, $E$2:$E$706, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O205" s="10"/>
@@ -10704,7 +10727,7 @@
         <v>118</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B206, $C$2:$C$706, C206, $D$2:$D$706, D206, $E$2:$E$706, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="30"/>
@@ -10751,7 +10774,7 @@
         <v>1000</v>
       </c>
       <c r="N207" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B207, $C$2:$C$706, C207, $D$2:$D$706, D207, $E$2:$E$706, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P207" s="30"/>
@@ -10788,7 +10811,7 @@
         <v>55</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B208, $C$2:$C$706, C208, $D$2:$D$706, D208, $E$2:$E$706, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10822,7 +10845,7 @@
       </c>
       <c r="J209" s="35"/>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B209, $C$2:$C$706, C209, $D$2:$D$706, D209, $E$2:$E$706, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10868,7 +10891,7 @@
         <v>651</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B210, $C$2:$C$706, C210, $D$2:$D$706, D210, $E$2:$E$706, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10914,7 +10937,7 @@
         <v>480</v>
       </c>
       <c r="N211" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B211, $C$2:$C$706, C211, $D$2:$D$706, D211, $E$2:$E$706, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10960,7 +10983,7 @@
         <v>47480</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B212, $C$2:$C$706, C212, $D$2:$D$706, D212, $E$2:$E$706, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11006,7 +11029,7 @@
         <v>360</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B213, $C$2:$C$706, C213, $D$2:$D$706, D213, $E$2:$E$706, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11042,7 +11065,7 @@
         <v>55</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B214, $C$2:$C$706, C214, $D$2:$D$706, D214, $E$2:$E$706, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11088,7 +11111,7 @@
         <v>340</v>
       </c>
       <c r="N215" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B215, $C$2:$C$706, C215, $D$2:$D$706, D215, $E$2:$E$706, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11122,7 +11145,7 @@
       </c>
       <c r="J216" s="35"/>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B216, $C$2:$C$706, C216, $D$2:$D$706, D216, $E$2:$E$706, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11158,7 +11181,7 @@
         <v>118</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B217, $C$2:$C$706, C217, $D$2:$D$706, D217, $E$2:$E$706, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11204,7 +11227,7 @@
         <v>250</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B218, $C$2:$C$706, C218, $D$2:$D$706, D218, $E$2:$E$706, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P218" s="30"/>
@@ -11251,7 +11274,7 @@
         <v>300</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B219, $C$2:$C$706, C219, $D$2:$D$706, D219, $E$2:$E$706, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11287,7 +11310,7 @@
         <v>117</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B220, $C$2:$C$706, C220, $D$2:$D$706, D220, $E$2:$E$706, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11321,7 +11344,7 @@
       </c>
       <c r="J221" s="35"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B221, $C$2:$C$706, C221, $D$2:$D$706, D221, $E$2:$E$706, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11367,7 +11390,7 @@
         <v>940</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B222, $C$2:$C$706, C222, $D$2:$D$706, D222, $E$2:$E$706, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11413,7 +11436,7 @@
         <v>300</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B223, $C$2:$C$706, C223, $D$2:$D$706, D223, $E$2:$E$706, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11459,7 +11482,7 @@
         <v>320</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B224, $C$2:$C$706, C224, $D$2:$D$706, D224, $E$2:$E$706, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11505,7 +11528,7 @@
         <v>448</v>
       </c>
       <c r="N225" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B225, $C$2:$C$706, C225, $D$2:$D$706, D225, $E$2:$E$706, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11541,7 +11564,7 @@
         <v>118</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B226, $C$2:$C$706, C226, $D$2:$D$706, D226, $E$2:$E$706, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11575,7 +11598,7 @@
       </c>
       <c r="J227" s="35"/>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B227, $C$2:$C$706, C227, $D$2:$D$706, D227, $E$2:$E$706, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11614,7 +11637,7 @@
         <v>146</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B228, $C$2:$C$706, C228, $D$2:$D$706, D228, $E$2:$E$706, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11650,7 +11673,7 @@
         <v>117</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B229, $C$2:$C$706, C229, $D$2:$D$706, D229, $E$2:$E$706, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11684,7 +11707,7 @@
       </c>
       <c r="J230" s="35"/>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B230, $C$2:$C$706, C230, $D$2:$D$706, D230, $E$2:$E$706, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11720,7 +11743,7 @@
         <v>118</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B231, $C$2:$C$706, C231, $D$2:$D$706, D231, $E$2:$E$706, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11761,7 +11784,7 @@
       <c r="L232" s="17"/>
       <c r="M232" s="17"/>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B232, $C$2:$C$706, C232, $D$2:$D$706, D232, $E$2:$E$706, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11795,7 +11818,7 @@
       </c>
       <c r="J233" s="35"/>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B233, $C$2:$C$706, C233, $D$2:$D$706, D233, $E$2:$E$706, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11831,7 +11854,7 @@
         <v>117</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B234, $C$2:$C$706, C234, $D$2:$D$706, D234, $E$2:$E$706, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P234" s="30"/>
@@ -11868,7 +11891,7 @@
         <v>117</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B235, $C$2:$C$706, C235, $D$2:$D$706, D235, $E$2:$E$706, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11914,7 +11937,7 @@
         <v>646</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B236, $C$2:$C$706, C236, $D$2:$D$706, D236, $E$2:$E$706, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="39" t="s">
@@ -11963,7 +11986,7 @@
         <v>400</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B237, $C$2:$C$706, C237, $D$2:$D$706, D237, $E$2:$E$706, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11997,7 +12020,7 @@
       </c>
       <c r="J238" s="35"/>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B238, $C$2:$C$706, C238, $D$2:$D$706, D238, $E$2:$E$706, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12043,7 +12066,7 @@
         <v>300</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B239, $C$2:$C$706, C239, $D$2:$D$706, D239, $E$2:$E$706, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12079,7 +12102,7 @@
         <v>118</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B240, $C$2:$C$706, C240, $D$2:$D$706, D240, $E$2:$E$706, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12115,7 +12138,7 @@
         <v>154</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B241, $C$2:$C$706, C241, $D$2:$D$706, D241, $E$2:$E$706, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12161,7 +12184,7 @@
         <v>1800</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B242, $C$2:$C$706, C242, $D$2:$D$706, D242, $E$2:$E$706, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12198,7 +12221,7 @@
       <c r="L243" s="18"/>
       <c r="M243" s="18"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B243, $C$2:$C$706, C243, $D$2:$D$706, D243, $E$2:$E$706, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="10"/>
@@ -12246,7 +12269,7 @@
         <v>260</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B244, $C$2:$C$706, C244, $D$2:$D$706, D244, $E$2:$E$706, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="10"/>
@@ -12284,7 +12307,7 @@
         <v>118</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B245, $C$2:$C$706, C245, $D$2:$D$706, D245, $E$2:$E$706, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12330,7 +12353,7 @@
         <v>800</v>
       </c>
       <c r="N246" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B246, $C$2:$C$706, C246, $D$2:$D$706, D246, $E$2:$E$706, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12364,7 +12387,7 @@
       </c>
       <c r="J247" s="35"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B247, $C$2:$C$706, C247, $D$2:$D$706, D247, $E$2:$E$706, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12400,7 +12423,7 @@
         <v>117</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B248, $C$2:$C$706, C248, $D$2:$D$706, D248, $E$2:$E$706, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12446,7 +12469,7 @@
         <v>650</v>
       </c>
       <c r="N249" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B249, $C$2:$C$706, C249, $D$2:$D$706, D249, $E$2:$E$706, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P249" s="30"/>
@@ -12493,7 +12516,7 @@
         <v>370</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B250, $C$2:$C$706, C250, $D$2:$D$706, D250, $E$2:$E$706, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P250" s="30"/>
@@ -12540,7 +12563,7 @@
         <v>235</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B251, $C$2:$C$706, C251, $D$2:$D$706, D251, $E$2:$E$706, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12574,7 +12597,7 @@
       </c>
       <c r="J252" s="35"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B252, $C$2:$C$706, C252, $D$2:$D$706, D252, $E$2:$E$706, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12610,7 +12633,7 @@
         <v>117</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B253, $C$2:$C$706, C253, $D$2:$D$706, D253, $E$2:$E$706, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12656,7 +12679,7 @@
         <v>650</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B254, $C$2:$C$706, C254, $D$2:$D$706, D254, $E$2:$E$706, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="30"/>
@@ -12703,7 +12726,7 @@
         <v>300</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B255, $C$2:$C$706, C255, $D$2:$D$706, D255, $E$2:$E$706, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12740,7 +12763,7 @@
       <c r="L256" s="18"/>
       <c r="M256" s="18"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B256, $C$2:$C$706, C256, $D$2:$D$706, D256, $E$2:$E$706, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="10"/>
@@ -12776,7 +12799,7 @@
       </c>
       <c r="J257" s="35"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B257, $C$2:$C$706, C257, $D$2:$D$706, D257, $E$2:$E$706, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="30"/>
@@ -12813,7 +12836,7 @@
         <v>118</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B258, $C$2:$C$706, C258, $D$2:$D$706, D258, $E$2:$E$706, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N297" si="12">IF(COUNTIFS( $B$2:$B$706, B258, $C$2:$C$706, C258, $D$2:$D$706, D258, $E$2:$E$706, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O258" s="30"/>
@@ -12850,7 +12873,7 @@
         <v>118</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B259, $C$2:$C$706, C259, $D$2:$D$706, D259, $E$2:$E$706, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12896,7 +12919,7 @@
         <v>500</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B260, $C$2:$C$706, C260, $D$2:$D$706, D260, $E$2:$E$706, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="39" t="s">
@@ -12934,7 +12957,7 @@
       </c>
       <c r="J261" s="35"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B261, $C$2:$C$706, C261, $D$2:$D$706, D261, $E$2:$E$706, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12980,7 +13003,7 @@
         <v>300</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B262, $C$2:$C$706, C262, $D$2:$D$706, D262, $E$2:$E$706, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13026,7 +13049,7 @@
         <v>268</v>
       </c>
       <c r="N263" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B263, $C$2:$C$706, C263, $D$2:$D$706, D263, $E$2:$E$706, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13062,7 +13085,7 @@
         <v>118</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B264, $C$2:$C$706, C264, $D$2:$D$706, D264, $E$2:$E$706, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13101,7 +13124,7 @@
       <c r="L265" s="18"/>
       <c r="M265" s="18"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B265, $C$2:$C$706, C265, $D$2:$D$706, D265, $E$2:$E$706, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="10"/>
@@ -13142,7 +13165,7 @@
       <c r="L266" s="18"/>
       <c r="M266" s="18"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B266, $C$2:$C$706, C266, $D$2:$D$706, D266, $E$2:$E$706, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="10"/>
@@ -13190,7 +13213,7 @@
         <v>285</v>
       </c>
       <c r="N267" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B267, $C$2:$C$706, C267, $D$2:$D$706, D267, $E$2:$E$706, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13236,7 +13259,7 @@
         <v>726</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B268, $C$2:$C$706, C268, $D$2:$D$706, D268, $E$2:$E$706, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13273,7 +13296,7 @@
       <c r="L269" s="18"/>
       <c r="M269" s="18"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B269, $C$2:$C$706, C269, $D$2:$D$706, D269, $E$2:$E$706, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O269" s="10"/>
@@ -13311,7 +13334,7 @@
         <v>117</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B270, $C$2:$C$706, C270, $D$2:$D$706, D270, $E$2:$E$706, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13345,7 +13368,7 @@
       </c>
       <c r="J271" s="35"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B271, $C$2:$C$706, C271, $D$2:$D$706, D271, $E$2:$E$706, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O271" s="30"/>
@@ -13383,7 +13406,7 @@
       <c r="L272" s="18"/>
       <c r="M272" s="18"/>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B272, $C$2:$C$706, C272, $D$2:$D$706, D272, $E$2:$E$706, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O272" s="10"/>
@@ -13431,7 +13454,7 @@
         <v>250</v>
       </c>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B273, $C$2:$C$706, C273, $D$2:$D$706, D273, $E$2:$E$706, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O273" s="10"/>
@@ -13467,7 +13490,7 @@
       </c>
       <c r="J274" s="35"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B274, $C$2:$C$706, C274, $D$2:$D$706, D274, $E$2:$E$706, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13513,7 +13536,7 @@
         <v>275</v>
       </c>
       <c r="N275" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B275, $C$2:$C$706, C275, $D$2:$D$706, D275, $E$2:$E$706, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13547,7 +13570,7 @@
       </c>
       <c r="J276" s="35"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B276, $C$2:$C$706, C276, $D$2:$D$706, D276, $E$2:$E$706, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13593,7 +13616,7 @@
         <v>300</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B277, $C$2:$C$706, C277, $D$2:$D$706, D277, $E$2:$E$706, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13627,7 +13650,7 @@
       </c>
       <c r="J278" s="35"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B278, $C$2:$C$706, C278, $D$2:$D$706, D278, $E$2:$E$706, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13673,7 +13696,7 @@
         <v>250</v>
       </c>
       <c r="N279" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B279, $C$2:$C$706, C279, $D$2:$D$706, D279, $E$2:$E$706, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="P279" s="30"/>
@@ -13710,7 +13733,7 @@
         <v>118</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B280, $C$2:$C$706, C280, $D$2:$D$706, D280, $E$2:$E$706, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13746,7 +13769,7 @@
         <v>118</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B281, $C$2:$C$706, C281, $D$2:$D$706, D281, $E$2:$E$706, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13780,7 +13803,7 @@
       </c>
       <c r="J282" s="35"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B282, $C$2:$C$706, C282, $D$2:$D$706, D282, $E$2:$E$706, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="P282" s="30"/>
@@ -13817,7 +13840,7 @@
         <v>118</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B283, $C$2:$C$706, C283, $D$2:$D$706, D283, $E$2:$E$706, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13851,7 +13874,7 @@
       </c>
       <c r="J284" s="35"/>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B284, $C$2:$C$706, C284, $D$2:$D$706, D284, $E$2:$E$706, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="P284" s="30"/>
@@ -13888,7 +13911,7 @@
         <v>118</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B285, $C$2:$C$706, C285, $D$2:$D$706, D285, $E$2:$E$706, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13922,7 +13945,7 @@
       </c>
       <c r="J286" s="35"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B286, $C$2:$C$706, C286, $D$2:$D$706, D286, $E$2:$E$706, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13968,7 +13991,7 @@
         <v>300</v>
       </c>
       <c r="N287" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B287, $C$2:$C$706, C287, $D$2:$D$706, D287, $E$2:$E$706, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14002,7 +14025,7 @@
       </c>
       <c r="J288" s="35"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B288, $C$2:$C$706, C288, $D$2:$D$706, D288, $E$2:$E$706, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14048,7 +14071,7 @@
         <v>250</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B289, $C$2:$C$706, C289, $D$2:$D$706, D289, $E$2:$E$706, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O289" s="10"/>
@@ -14087,7 +14110,7 @@
       <c r="L290" s="18"/>
       <c r="M290" s="18"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B290, $C$2:$C$706, C290, $D$2:$D$706, D290, $E$2:$E$706, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O290" s="10"/>
@@ -14123,7 +14146,7 @@
       </c>
       <c r="J291" s="35"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B291, $C$2:$C$706, C291, $D$2:$D$706, D291, $E$2:$E$706, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14159,7 +14182,7 @@
         <v>55</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B292, $C$2:$C$706, C292, $D$2:$D$706, D292, $E$2:$E$706, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14195,7 +14218,7 @@
         <v>118</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B293, $C$2:$C$706, C293, $D$2:$D$706, D293, $E$2:$E$706, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14229,7 +14252,7 @@
       </c>
       <c r="J294" s="35"/>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B294, $C$2:$C$706, C294, $D$2:$D$706, D294, $E$2:$E$706, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14268,7 +14291,7 @@
       <c r="L295" s="28"/>
       <c r="M295" s="28"/>
       <c r="N295" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B295, $C$2:$C$706, C295, $D$2:$D$706, D295, $E$2:$E$706, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O295" s="30"/>
@@ -14309,7 +14332,7 @@
       <c r="L296" s="28"/>
       <c r="M296" s="28"/>
       <c r="N296" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B296, $C$2:$C$706, C296, $D$2:$D$706, D296, $E$2:$E$706, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O296" s="30"/>
@@ -14347,7 +14370,7 @@
         <v>117</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B297, $C$2:$C$706, C297, $D$2:$D$706, D297, $E$2:$E$706, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21929,8 +21952,8 @@
     <filterColumn colId="14">
       <filters blank="1"/>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P297">
-      <sortCondition ref="F1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P115">
+      <sortCondition descending="1" ref="F1:F297"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -22271,7 +22294,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B2, $C$2:$C$706, C2, $D$2:$D$706, D2, $E$2:$E$706, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$706, B2, $C$2:$C$706, C2, $D$2:$D$706, D2, $E$2:$E$706, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -22312,7 +22335,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B3, $C$2:$C$706, C3, $D$2:$D$706, D3, $E$2:$E$706, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -22356,7 +22379,7 @@
         <v>3156</v>
       </c>
       <c r="N4" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B4, $C$2:$C$706, C4, $D$2:$D$706, D4, $E$2:$E$706, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -22404,7 +22427,7 @@
         <v>34175</v>
       </c>
       <c r="N5" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B5, $C$2:$C$706, C5, $D$2:$D$706, D5, $E$2:$E$706, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -22445,7 +22468,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B6, $C$2:$C$706, C6, $D$2:$D$706, D6, $E$2:$E$706, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -22486,7 +22509,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B7, $C$2:$C$706, C7, $D$2:$D$706, D7, $E$2:$E$706, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -22525,7 +22548,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B8, $C$2:$C$706, C8, $D$2:$D$706, D8, $E$2:$E$706, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="25"/>
@@ -22573,7 +22596,7 @@
         <v>350</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B9, $C$2:$C$706, C9, $D$2:$D$706, D9, $E$2:$E$706, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -22612,7 +22635,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B10, $C$2:$C$706, C10, $D$2:$D$706, D10, $E$2:$E$706, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="19"/>
@@ -22660,7 +22683,7 @@
         <v>300</v>
       </c>
       <c r="N11" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B11, $C$2:$C$706, C11, $D$2:$D$706, D11, $E$2:$E$706, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O11" s="30"/>
@@ -22708,7 +22731,7 @@
         <v>200</v>
       </c>
       <c r="N12" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B12, $C$2:$C$706, C12, $D$2:$D$706, D12, $E$2:$E$706, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O12" s="30"/>
@@ -22747,7 +22770,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B13, $C$2:$C$706, C13, $D$2:$D$706, D13, $E$2:$E$706, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -22788,7 +22811,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B14, $C$2:$C$706, C14, $D$2:$D$706, D14, $E$2:$E$706, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22834,7 +22857,7 @@
         <v>500</v>
       </c>
       <c r="N15" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B15, $C$2:$C$706, C15, $D$2:$D$706, D15, $E$2:$E$706, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="10"/>
@@ -22882,7 +22905,7 @@
         <v>700</v>
       </c>
       <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B16, $C$2:$C$706, C16, $D$2:$D$706, D16, $E$2:$E$706, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="10"/>
@@ -22923,7 +22946,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B17, $C$2:$C$706, C17, $D$2:$D$706, D17, $E$2:$E$706, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="10"/>
@@ -22971,7 +22994,7 @@
         <v>650</v>
       </c>
       <c r="N18" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B18, $C$2:$C$706, C18, $D$2:$D$706, D18, $E$2:$E$706, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23008,7 +23031,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B19, $C$2:$C$706, C19, $D$2:$D$706, D19, $E$2:$E$706, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23054,7 +23077,7 @@
         <v>516</v>
       </c>
       <c r="N20" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B20, $C$2:$C$706, C20, $D$2:$D$706, D20, $E$2:$E$706, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23100,7 +23123,7 @@
         <v>720</v>
       </c>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B21, $C$2:$C$706, C21, $D$2:$D$706, D21, $E$2:$E$706, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23146,7 +23169,7 @@
         <v>300</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B22, $C$2:$C$706, C22, $D$2:$D$706, D22, $E$2:$E$706, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P22" s="24"/>
@@ -23186,7 +23209,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B23, $C$2:$C$706, C23, $D$2:$D$706, D23, $E$2:$E$706, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
@@ -23227,7 +23250,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B24, $C$2:$C$706, C24, $D$2:$D$706, D24, $E$2:$E$706, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -23268,7 +23291,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B25, $C$2:$C$706, C25, $D$2:$D$706, D25, $E$2:$E$706, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23307,7 +23330,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B26, $C$2:$C$706, C26, $D$2:$D$706, D26, $E$2:$E$706, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23353,7 +23376,7 @@
         <v>650</v>
       </c>
       <c r="N27" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B27, $C$2:$C$706, C27, $D$2:$D$706, D27, $E$2:$E$706, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23400,7 +23423,7 @@
         <v>175</v>
       </c>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B28, $C$2:$C$706, C28, $D$2:$D$706, D28, $E$2:$E$706, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="10"/>
@@ -23448,7 +23471,7 @@
         <v>300</v>
       </c>
       <c r="N29" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B29, $C$2:$C$706, C29, $D$2:$D$706, D29, $E$2:$E$706, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23487,7 +23510,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B30, $C$2:$C$706, C30, $D$2:$D$706, D30, $E$2:$E$706, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -23526,7 +23549,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B31, $C$2:$C$706, C31, $D$2:$D$706, D31, $E$2:$E$706, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -23566,7 +23589,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B32, $C$2:$C$706, C32, $D$2:$D$706, D32, $E$2:$E$706, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -23607,7 +23630,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B33, $C$2:$C$706, C33, $D$2:$D$706, D33, $E$2:$E$706, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -23646,7 +23669,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B34, $C$2:$C$706, C34, $D$2:$D$706, D34, $E$2:$E$706, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -23686,7 +23709,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B35, $C$2:$C$706, C35, $D$2:$D$706, D35, $E$2:$E$706, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -23725,7 +23748,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B36, $C$2:$C$706, C36, $D$2:$D$706, D36, $E$2:$E$706, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -23774,7 +23797,7 @@
         <v>225</v>
       </c>
       <c r="N37" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B37, $C$2:$C$706, C37, $D$2:$D$706, D37, $E$2:$E$706, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23820,7 +23843,7 @@
         <v>300</v>
       </c>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B38, $C$2:$C$706, C38, $D$2:$D$706, D38, $E$2:$E$706, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23859,7 +23882,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B39, $C$2:$C$706, C39, $D$2:$D$706, D39, $E$2:$E$706, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P39"/>
@@ -23897,7 +23920,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B40, $C$2:$C$706, C40, $D$2:$D$706, D40, $E$2:$E$706, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -23938,7 +23961,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B41, $C$2:$C$706, C41, $D$2:$D$706, D41, $E$2:$E$706, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -23979,7 +24002,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B42, $C$2:$C$706, C42, $D$2:$D$706, D42, $E$2:$E$706, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -24028,7 +24051,7 @@
         <v>540</v>
       </c>
       <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B43, $C$2:$C$706, C43, $D$2:$D$706, D43, $E$2:$E$706, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -24067,7 +24090,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B44, $C$2:$C$706, C44, $D$2:$D$706, D44, $E$2:$E$706, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -24108,7 +24131,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B45, $C$2:$C$706, C45, $D$2:$D$706, D45, $E$2:$E$706, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -24147,7 +24170,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B46, $C$2:$C$706, C46, $D$2:$D$706, D46, $E$2:$E$706, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -24195,7 +24218,7 @@
         <v>314</v>
       </c>
       <c r="N47" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B47, $C$2:$C$706, C47, $D$2:$D$706, D47, $E$2:$E$706, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24234,7 +24257,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B48, $C$2:$C$706, C48, $D$2:$D$706, D48, $E$2:$E$706, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -24272,7 +24295,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B49, $C$2:$C$706, C49, $D$2:$D$706, D49, $E$2:$E$706, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -24311,7 +24334,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B50, $C$2:$C$706, C50, $D$2:$D$706, D50, $E$2:$E$706, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -24350,7 +24373,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B51, $C$2:$C$706, C51, $D$2:$D$706, D51, $E$2:$E$706, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -24391,7 +24414,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B52, $C$2:$C$706, C52, $D$2:$D$706, D52, $E$2:$E$706, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -24430,7 +24453,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B53, $C$2:$C$706, C53, $D$2:$D$706, D53, $E$2:$E$706, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -24478,7 +24501,7 @@
         <v>240</v>
       </c>
       <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B54, $C$2:$C$706, C54, $D$2:$D$706, D54, $E$2:$E$706, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54" s="10"/>
@@ -24526,7 +24549,7 @@
         <v>300</v>
       </c>
       <c r="N55" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B55, $C$2:$C$706, C55, $D$2:$D$706, D55, $E$2:$E$706, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -24565,7 +24588,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B56, $C$2:$C$706, C56, $D$2:$D$706, D56, $E$2:$E$706, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -24604,7 +24627,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B57, $C$2:$C$706, C57, $D$2:$D$706, D57, $E$2:$E$706, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24645,7 +24668,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B58, $C$2:$C$706, C58, $D$2:$D$706, D58, $E$2:$E$706, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24682,7 +24705,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B59, $C$2:$C$706, C59, $D$2:$D$706, D59, $E$2:$E$706, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24728,7 +24751,7 @@
         <v>250</v>
       </c>
       <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B60, $C$2:$C$706, C60, $D$2:$D$706, D60, $E$2:$E$706, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="10"/>
@@ -24767,7 +24790,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B61, $C$2:$C$706, C61, $D$2:$D$706, D61, $E$2:$E$706, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24804,7 +24827,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B62, $C$2:$C$706, C62, $D$2:$D$706, D62, $E$2:$E$706, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24843,7 +24866,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B63, $C$2:$C$706, C63, $D$2:$D$706, D63, $E$2:$E$706, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -24884,7 +24907,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B64, $C$2:$C$706, C64, $D$2:$D$706, D64, $E$2:$E$706, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -24923,7 +24946,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B65, $C$2:$C$706, C65, $D$2:$D$706, D65, $E$2:$E$706, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -24962,7 +24985,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B66, $C$2:$C$706, C66, $D$2:$D$706, D66, $E$2:$E$706, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$706, B66, $C$2:$C$706, C66, $D$2:$D$706, D66, $E$2:$E$706, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -25010,7 +25033,7 @@
         <v>302</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B67, $C$2:$C$706, C67, $D$2:$D$706, D67, $E$2:$E$706, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25049,7 +25072,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B68, $C$2:$C$706, C68, $D$2:$D$706, D68, $E$2:$E$706, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -25097,7 +25120,7 @@
         <v>10680</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B69, $C$2:$C$706, C69, $D$2:$D$706, D69, $E$2:$E$706, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25136,7 +25159,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B70, $C$2:$C$706, C70, $D$2:$D$706, D70, $E$2:$E$706, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -25184,7 +25207,7 @@
         <v>10880</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B71, $C$2:$C$706, C71, $D$2:$D$706, D71, $E$2:$E$706, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25223,7 +25246,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B72, $C$2:$C$706, C72, $D$2:$D$706, D72, $E$2:$E$706, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -25271,7 +25294,7 @@
         <v>300</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B73, $C$2:$C$706, C73, $D$2:$D$706, D73, $E$2:$E$706, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="39" t="s">
@@ -25314,7 +25337,7 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B74, $C$2:$C$706, C74, $D$2:$D$706, D74, $E$2:$E$706, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
@@ -25362,7 +25385,7 @@
         <v>1200</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B75, $C$2:$C$706, C75, $D$2:$D$706, D75, $E$2:$E$706, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25399,7 +25422,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B76, $C$2:$C$706, C76, $D$2:$D$706, D76, $E$2:$E$706, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76"/>
@@ -25447,7 +25470,7 @@
         <v>300</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B77, $C$2:$C$706, C77, $D$2:$D$706, D77, $E$2:$E$706, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="39" t="s">
@@ -25489,7 +25512,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B78, $C$2:$C$706, C78, $D$2:$D$706, D78, $E$2:$E$706, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
@@ -25538,7 +25561,7 @@
         <v>300</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B79, $C$2:$C$706, C79, $D$2:$D$706, D79, $E$2:$E$706, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25584,7 +25607,7 @@
         <v>646</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B80, $C$2:$C$706, C80, $D$2:$D$706, D80, $E$2:$E$706, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="39" t="s">
@@ -25633,7 +25656,7 @@
         <v>300</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B81, $C$2:$C$706, C81, $D$2:$D$706, D81, $E$2:$E$706, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="10"/>
@@ -25681,7 +25704,7 @@
         <v>300</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B82, $C$2:$C$706, C82, $D$2:$D$706, D82, $E$2:$E$706, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25727,7 +25750,7 @@
         <v>18850</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B83, $C$2:$C$706, C83, $D$2:$D$706, D83, $E$2:$E$706, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25761,7 +25784,7 @@
       </c>
       <c r="J84" s="35"/>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B84, $C$2:$C$706, C84, $D$2:$D$706, D84, $E$2:$E$706, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25803,11 +25826,11 @@
         <v>5585</v>
       </c>
       <c r="M85" s="28">
-        <f t="shared" ref="M85:M92" si="0">ABS((D85*E85)-L85)</f>
+        <f t="shared" ref="M85:M92" si="2">ABS((D85*E85)-L85)</f>
         <v>395</v>
       </c>
       <c r="N85" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B85, $C$2:$C$706, C85, $D$2:$D$706, D85, $E$2:$E$706, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O85" s="39" t="s">
@@ -25853,11 +25876,11 @@
         <v>5730</v>
       </c>
       <c r="M86" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="N86" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B86, $C$2:$C$706, C86, $D$2:$D$706, D86, $E$2:$E$706, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O86" s="39" t="s">
@@ -25903,11 +25926,11 @@
         <v>32900</v>
       </c>
       <c r="M87" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B87, $C$2:$C$706, C87, $D$2:$D$706, D87, $E$2:$E$706, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25949,11 +25972,11 @@
         <v>19730.5</v>
       </c>
       <c r="M88" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>504.5</v>
       </c>
       <c r="N88" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B88, $C$2:$C$706, C88, $D$2:$D$706, D88, $E$2:$E$706, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O88" s="39" t="s">
@@ -25998,11 +26021,11 @@
         <v>19690</v>
       </c>
       <c r="M89" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>545</v>
       </c>
       <c r="N89" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B89, $C$2:$C$706, C89, $D$2:$D$706, D89, $E$2:$E$706, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O89" s="39" t="s">
@@ -26047,11 +26070,11 @@
         <v>9170</v>
       </c>
       <c r="M90" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B90, $C$2:$C$706, C90, $D$2:$D$706, D90, $E$2:$E$706, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="39" t="s">
@@ -26096,11 +26119,11 @@
         <v>8220</v>
       </c>
       <c r="M91" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B91, $C$2:$C$706, C91, $D$2:$D$706, D91, $E$2:$E$706, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="39" t="s">
@@ -26145,11 +26168,11 @@
         <v>6367.2</v>
       </c>
       <c r="M92" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B92, $C$2:$C$706, C92, $D$2:$D$706, D92, $E$2:$E$706, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O92" s="39" t="s">
@@ -26191,7 +26214,7 @@
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B93, $C$2:$C$706, C93, $D$2:$D$706, D93, $E$2:$E$706, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93"/>
@@ -26235,11 +26258,11 @@
         <v>16755</v>
       </c>
       <c r="M94" s="18">
-        <f t="shared" ref="M94:M102" si="1">ABS((D94*E94)-L94)</f>
+        <f t="shared" ref="M94:M102" si="3">ABS((D94*E94)-L94)</f>
         <v>295</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B94, $C$2:$C$706, C94, $D$2:$D$706, D94, $E$2:$E$706, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26281,11 +26304,11 @@
         <v>5755</v>
       </c>
       <c r="M95" s="28">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+      <c r="N95" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>275</v>
-      </c>
-      <c r="N95" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B95, $C$2:$C$706, C95, $D$2:$D$706, D95, $E$2:$E$706, E95) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -26327,11 +26350,11 @@
         <v>5805</v>
       </c>
       <c r="M96" s="28">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="N96" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>225</v>
-      </c>
-      <c r="N96" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B96, $C$2:$C$706, C96, $D$2:$D$706, D96, $E$2:$E$706, E96) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -26373,11 +26396,11 @@
         <v>10400</v>
       </c>
       <c r="M97" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N97" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B97, $C$2:$C$706, C97, $D$2:$D$706, D97, $E$2:$E$706, E97) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26420,11 +26443,11 @@
         <v>3160</v>
       </c>
       <c r="M98" s="18">
+        <f t="shared" si="3"/>
+        <v>235</v>
+      </c>
+      <c r="N98" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>235</v>
-      </c>
-      <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B98, $C$2:$C$706, C98, $D$2:$D$706, D98, $E$2:$E$706, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26466,11 +26489,11 @@
         <v>3300</v>
       </c>
       <c r="M99" s="18">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="N99" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B99, $C$2:$C$706, C99, $D$2:$D$706, D99, $E$2:$E$706, E99) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26512,11 +26535,11 @@
         <v>14130</v>
       </c>
       <c r="M100" s="18">
+        <f t="shared" si="3"/>
+        <v>714</v>
+      </c>
+      <c r="N100" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>714</v>
-      </c>
-      <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B100, $C$2:$C$706, C100, $D$2:$D$706, D100, $E$2:$E$706, E100) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O100" s="10"/>
@@ -26560,11 +26583,11 @@
         <v>9170</v>
       </c>
       <c r="M101" s="28">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N101" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B101, $C$2:$C$706, C101, $D$2:$D$706, D101, $E$2:$E$706, E101) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26606,11 +26629,11 @@
         <v>20010</v>
       </c>
       <c r="M102" s="18">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="N102" t="str">
         <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="N102" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B102, $C$2:$C$706, C102, $D$2:$D$706, D102, $E$2:$E$706, E102) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P102"/>
@@ -26647,7 +26670,7 @@
         <v>118</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B103, $C$2:$C$706, C103, $D$2:$D$706, D103, $E$2:$E$706, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26689,11 +26712,11 @@
         <v>33200</v>
       </c>
       <c r="M104" s="18">
-        <f t="shared" ref="M104:M110" si="2">ABS((D104*E104)-L104)</f>
+        <f t="shared" ref="M104:M110" si="4">ABS((D104*E104)-L104)</f>
         <v>1200</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B104, $C$2:$C$706, C104, $D$2:$D$706, D104, $E$2:$E$706, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26735,11 +26758,11 @@
         <v>10249</v>
       </c>
       <c r="M105" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4451</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B105, $C$2:$C$706, C105, $D$2:$D$706, D105, $E$2:$E$706, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="39" t="s">
@@ -26785,11 +26808,11 @@
         <v>20260</v>
       </c>
       <c r="M106" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N106" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B106, $C$2:$C$706, C106, $D$2:$D$706, D106, $E$2:$E$706, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106"/>
@@ -26833,11 +26856,11 @@
         <v>39300</v>
       </c>
       <c r="M107" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18350</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B107, $C$2:$C$706, C107, $D$2:$D$706, D107, $E$2:$E$706, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26879,11 +26902,11 @@
         <v>4120</v>
       </c>
       <c r="M108" s="28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="N108" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B108, $C$2:$C$706, C108, $D$2:$D$706, D108, $E$2:$E$706, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108" s="40" t="s">
@@ -26929,11 +26952,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M109" s="28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N109" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B109, $C$2:$C$706, C109, $D$2:$D$706, D109, $E$2:$E$706, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="40" t="s">
@@ -26979,11 +27002,11 @@
         <v>8420</v>
       </c>
       <c r="M110" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B110, $C$2:$C$706, C110, $D$2:$D$706, D110, $E$2:$E$706, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27017,7 +27040,7 @@
       </c>
       <c r="J111" s="35"/>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B111, $C$2:$C$706, C111, $D$2:$D$706, D111, $E$2:$E$706, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27059,11 +27082,11 @@
         <v>14100</v>
       </c>
       <c r="M112" s="18">
-        <f t="shared" ref="M112:M122" si="3">ABS((D112*E112)-L112)</f>
+        <f t="shared" ref="M112:M122" si="5">ABS((D112*E112)-L112)</f>
         <v>500</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B112, $C$2:$C$706, C112, $D$2:$D$706, D112, $E$2:$E$706, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27105,11 +27128,11 @@
         <v>9270</v>
       </c>
       <c r="M113" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B113, $C$2:$C$706, C113, $D$2:$D$706, D113, $E$2:$E$706, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P113" s="19"/>
@@ -27152,11 +27175,11 @@
         <v>5940</v>
       </c>
       <c r="M114" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B114, $C$2:$C$706, C114, $D$2:$D$706, D114, $E$2:$E$706, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27198,11 +27221,11 @@
         <v>15075</v>
       </c>
       <c r="M115" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>645</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B115, $C$2:$C$706, C115, $D$2:$D$706, D115, $E$2:$E$706, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O115" s="39" t="s">
@@ -27247,11 +27270,11 @@
         <v>33950</v>
       </c>
       <c r="M116" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>850</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B116, $C$2:$C$706, C116, $D$2:$D$706, D116, $E$2:$E$706, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27293,11 +27316,11 @@
         <v>9886</v>
       </c>
       <c r="M117" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>654</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B117, $C$2:$C$706, C117, $D$2:$D$706, D117, $E$2:$E$706, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27339,11 +27362,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M118" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>710.99999999999636</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B118, $C$2:$C$706, C118, $D$2:$D$706, D118, $E$2:$E$706, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="10"/>
@@ -27387,11 +27410,11 @@
         <v>17150</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B119, $C$2:$C$706, C119, $D$2:$D$706, D119, $E$2:$E$706, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="10"/>
@@ -27435,11 +27458,11 @@
         <v>8700</v>
       </c>
       <c r="M120" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B120, $C$2:$C$706, C120, $D$2:$D$706, D120, $E$2:$E$706, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27481,11 +27504,11 @@
         <v>14200</v>
       </c>
       <c r="M121" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B121, $C$2:$C$706, C121, $D$2:$D$706, D121, $E$2:$E$706, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27527,11 +27550,11 @@
         <v>5905</v>
       </c>
       <c r="M122" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>275</v>
       </c>
       <c r="N122" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B122, $C$2:$C$706, C122, $D$2:$D$706, D122, $E$2:$E$706, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27565,7 +27588,7 @@
       </c>
       <c r="J123" s="35"/>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B123, $C$2:$C$706, C123, $D$2:$D$706, D123, $E$2:$E$706, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="39" t="s">
@@ -27615,7 +27638,7 @@
         <v>280</v>
       </c>
       <c r="N124" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B124, $C$2:$C$706, C124, $D$2:$D$706, D124, $E$2:$E$706, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="39" t="s">
@@ -27664,7 +27687,7 @@
         <v>300</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B125, $C$2:$C$706, C125, $D$2:$D$706, D125, $E$2:$E$706, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27698,7 +27721,7 @@
       </c>
       <c r="J126" s="35"/>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B126, $C$2:$C$706, C126, $D$2:$D$706, D126, $E$2:$E$706, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="24"/>
@@ -27735,7 +27758,7 @@
         <v>118</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B127, $C$2:$C$706, C127, $D$2:$D$706, D127, $E$2:$E$706, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27781,7 +27804,7 @@
         <v>48320</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B128, $C$2:$C$706, C128, $D$2:$D$706, D128, $E$2:$E$706, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="39" t="s">
@@ -27830,7 +27853,7 @@
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B129, $C$2:$C$706, C129, $D$2:$D$706, D129, $E$2:$E$706, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P129" s="30"/>
@@ -27877,7 +27900,7 @@
         <v>650</v>
       </c>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B130, $C$2:$C$706, C130, $D$2:$D$706, D130, $E$2:$E$706, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$706, B130, $C$2:$C$706, C130, $D$2:$D$706, D130, $E$2:$E$706, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="39" t="s">
@@ -27926,7 +27949,7 @@
         <v>250</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B131, $C$2:$C$706, C131, $D$2:$D$706, D131, $E$2:$E$706, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="10"/>
@@ -27967,7 +27990,7 @@
         <v>145</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B132, $C$2:$C$706, C132, $D$2:$D$706, D132, $E$2:$E$706, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28009,11 +28032,11 @@
         <v>14440</v>
       </c>
       <c r="M133" s="18">
-        <f t="shared" ref="M133:M142" si="4">ABS((D133*E133)-L133)</f>
+        <f t="shared" ref="M133:M142" si="7">ABS((D133*E133)-L133)</f>
         <v>300</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B133, $C$2:$C$706, C133, $D$2:$D$706, D133, $E$2:$E$706, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O133"/>
@@ -28056,11 +28079,11 @@
         <v>16500</v>
       </c>
       <c r="M134" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1400</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B134, $C$2:$C$706, C134, $D$2:$D$706, D134, $E$2:$E$706, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="39" t="s">
@@ -28105,11 +28128,11 @@
         <v>14400</v>
       </c>
       <c r="M135" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B135, $C$2:$C$706, C135, $D$2:$D$706, D135, $E$2:$E$706, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28151,11 +28174,11 @@
         <v>18800</v>
       </c>
       <c r="M136" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B136, $C$2:$C$706, C136, $D$2:$D$706, D136, $E$2:$E$706, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="40" t="s">
@@ -28201,11 +28224,11 @@
         <v>6105</v>
       </c>
       <c r="M137" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="N137" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B137, $C$2:$C$706, C137, $D$2:$D$706, D137, $E$2:$E$706, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28247,11 +28270,11 @@
         <v>6005</v>
       </c>
       <c r="M138" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
       <c r="N138" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B138, $C$2:$C$706, C138, $D$2:$D$706, D138, $E$2:$E$706, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28293,11 +28316,11 @@
         <v>9470</v>
       </c>
       <c r="M139" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B139, $C$2:$C$706, C139, $D$2:$D$706, D139, $E$2:$E$706, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28339,11 +28362,11 @@
         <v>5370</v>
       </c>
       <c r="M140" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>320</v>
       </c>
       <c r="N140" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B140, $C$2:$C$706, C140, $D$2:$D$706, D140, $E$2:$E$706, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="30"/>
@@ -28387,11 +28410,11 @@
         <v>2610</v>
       </c>
       <c r="M141" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>235</v>
       </c>
       <c r="N141" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B141, $C$2:$C$706, C141, $D$2:$D$706, D141, $E$2:$E$706, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="30"/>
@@ -28435,11 +28458,11 @@
         <v>10410</v>
       </c>
       <c r="M142" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B142, $C$2:$C$706, C142, $D$2:$D$706, D142, $E$2:$E$706, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="30"/>
@@ -28476,7 +28499,7 @@
         <v>118</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B143, $C$2:$C$706, C143, $D$2:$D$706, D143, $E$2:$E$706, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P143"/>
@@ -28523,7 +28546,7 @@
         <v>501</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B144, $C$2:$C$706, C144, $D$2:$D$706, D144, $E$2:$E$706, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="39" t="s">
@@ -28563,7 +28586,7 @@
         <v>118</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B145, $C$2:$C$706, C145, $D$2:$D$706, D145, $E$2:$E$706, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28597,7 +28620,7 @@
       </c>
       <c r="J146" s="35"/>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B146, $C$2:$C$706, C146, $D$2:$D$706, D146, $E$2:$E$706, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="30"/>
@@ -28640,11 +28663,11 @@
         <v>73800</v>
       </c>
       <c r="M147" s="18">
-        <f t="shared" ref="M147:M160" si="5">ABS((D147*E147)-L147)</f>
+        <f t="shared" ref="M147:M160" si="8">ABS((D147*E147)-L147)</f>
         <v>47900</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B147, $C$2:$C$706, C147, $D$2:$D$706, D147, $E$2:$E$706, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O147" s="39" t="s">
@@ -28689,11 +28712,11 @@
         <v>7578</v>
       </c>
       <c r="M148" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>294</v>
       </c>
       <c r="N148" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B148, $C$2:$C$706, C148, $D$2:$D$706, D148, $E$2:$E$706, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28735,11 +28758,11 @@
         <v>7578</v>
       </c>
       <c r="M149" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>294</v>
       </c>
       <c r="N149" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B149, $C$2:$C$706, C149, $D$2:$D$706, D149, $E$2:$E$706, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O149" s="10"/>
@@ -28783,11 +28806,11 @@
         <v>4968</v>
       </c>
       <c r="M150" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>280</v>
       </c>
       <c r="N150" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B150, $C$2:$C$706, C150, $D$2:$D$706, D150, $E$2:$E$706, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28829,11 +28852,11 @@
         <v>4080</v>
       </c>
       <c r="M151" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B151, $C$2:$C$706, C151, $D$2:$D$706, D151, $E$2:$E$706, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28875,11 +28898,11 @@
         <v>34100</v>
       </c>
       <c r="M152" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1700</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B152, $C$2:$C$706, C152, $D$2:$D$706, D152, $E$2:$E$706, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="30"/>
@@ -28922,11 +28945,11 @@
         <v>25300</v>
       </c>
       <c r="M153" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B153, $C$2:$C$706, C153, $D$2:$D$706, D153, $E$2:$E$706, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="39" t="s">
@@ -28971,11 +28994,11 @@
         <v>12480</v>
       </c>
       <c r="M154" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>495</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B154, $C$2:$C$706, C154, $D$2:$D$706, D154, $E$2:$E$706, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="39" t="s">
@@ -29020,11 +29043,11 @@
         <v>18140</v>
       </c>
       <c r="M155" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N155" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B155, $C$2:$C$706, C155, $D$2:$D$706, D155, $E$2:$E$706, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29066,11 +29089,11 @@
         <v>14650</v>
       </c>
       <c r="M156" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>450</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B156, $C$2:$C$706, C156, $D$2:$D$706, D156, $E$2:$E$706, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29112,11 +29135,11 @@
         <v>10510</v>
       </c>
       <c r="M157" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B157, $C$2:$C$706, C157, $D$2:$D$706, D157, $E$2:$E$706, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29158,11 +29181,11 @@
         <v>12510</v>
       </c>
       <c r="M158" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>290</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B158, $C$2:$C$706, C158, $D$2:$D$706, D158, $E$2:$E$706, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29204,11 +29227,11 @@
         <v>16580</v>
       </c>
       <c r="M159" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>660</v>
       </c>
       <c r="N159" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B159, $C$2:$C$706, C159, $D$2:$D$706, D159, $E$2:$E$706, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="24"/>
@@ -29254,11 +29277,11 @@
         <v>2105</v>
       </c>
       <c r="M160" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N160" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B160, $C$2:$C$706, C160, $D$2:$D$706, D160, $E$2:$E$706, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="10"/>
@@ -29297,7 +29320,7 @@
       <c r="L161" s="18"/>
       <c r="M161" s="18"/>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B161, $C$2:$C$706, C161, $D$2:$D$706, D161, $E$2:$E$706, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="10"/>
@@ -29335,7 +29358,7 @@
         <v>117</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B162, $C$2:$C$706, C162, $D$2:$D$706, D162, $E$2:$E$706, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29381,7 +29404,7 @@
         <v>300</v>
       </c>
       <c r="N163" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B163, $C$2:$C$706, C163, $D$2:$D$706, D163, $E$2:$E$706, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O163" s="39" t="s">
@@ -29431,7 +29454,7 @@
         <v>300</v>
       </c>
       <c r="N164" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B164, $C$2:$C$706, C164, $D$2:$D$706, D164, $E$2:$E$706, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29465,7 +29488,7 @@
       </c>
       <c r="J165" s="35"/>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B165, $C$2:$C$706, C165, $D$2:$D$706, D165, $E$2:$E$706, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29507,11 +29530,11 @@
         <v>25530</v>
       </c>
       <c r="M166" s="18">
-        <f t="shared" ref="M166:M172" si="6">ABS((D166*E166)-L166)</f>
+        <f t="shared" ref="M166:M172" si="9">ABS((D166*E166)-L166)</f>
         <v>650</v>
       </c>
       <c r="N166" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B166, $C$2:$C$706, C166, $D$2:$D$706, D166, $E$2:$E$706, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O166"/>
@@ -29555,11 +29578,11 @@
         <v>5520</v>
       </c>
       <c r="M167" s="28">
+        <f t="shared" si="9"/>
+        <v>300</v>
+      </c>
+      <c r="N167" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>300</v>
-      </c>
-      <c r="N167" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B167, $C$2:$C$706, C167, $D$2:$D$706, D167, $E$2:$E$706, E167) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O167" s="39" t="s">
@@ -29604,11 +29627,11 @@
         <v>2657</v>
       </c>
       <c r="M168" s="28">
+        <f t="shared" si="9"/>
+        <v>253</v>
+      </c>
+      <c r="N168" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>253</v>
-      </c>
-      <c r="N168" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B168, $C$2:$C$706, C168, $D$2:$D$706, D168, $E$2:$E$706, E168) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O168" s="39" t="s">
@@ -29653,11 +29676,11 @@
         <v>2554.5</v>
       </c>
       <c r="M169" s="28">
+        <f t="shared" si="9"/>
+        <v>355.5</v>
+      </c>
+      <c r="N169" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>355.5</v>
-      </c>
-      <c r="N169" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B169, $C$2:$C$706, C169, $D$2:$D$706, D169, $E$2:$E$706, E169) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O169" s="39" t="s">
@@ -29703,11 +29726,11 @@
         <v>8820</v>
       </c>
       <c r="M170" s="28">
+        <f t="shared" si="9"/>
+        <v>650</v>
+      </c>
+      <c r="N170" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>650</v>
-      </c>
-      <c r="N170" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B170, $C$2:$C$706, C170, $D$2:$D$706, D170, $E$2:$E$706, E170) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O170" s="30"/>
@@ -29751,11 +29774,11 @@
         <v>36946</v>
       </c>
       <c r="M171" s="28">
+        <f t="shared" si="9"/>
+        <v>934</v>
+      </c>
+      <c r="N171" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>934</v>
-      </c>
-      <c r="N171" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B171, $C$2:$C$706, C171, $D$2:$D$706, D171, $E$2:$E$706, E171) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O171" s="30"/>
@@ -29799,11 +29822,11 @@
         <v>8049</v>
       </c>
       <c r="M172" s="18">
+        <f t="shared" si="9"/>
+        <v>800</v>
+      </c>
+      <c r="N172" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>800</v>
-      </c>
-      <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B172, $C$2:$C$706, C172, $D$2:$D$706, D172, $E$2:$E$706, E172) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O172" s="39" t="s">
@@ -29841,7 +29864,7 @@
       </c>
       <c r="J173" s="35"/>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B173, $C$2:$C$706, C173, $D$2:$D$706, D173, $E$2:$E$706, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29877,7 +29900,7 @@
         <v>117</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B174, $C$2:$C$706, C174, $D$2:$D$706, D174, $E$2:$E$706, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29923,7 +29946,7 @@
         <v>300</v>
       </c>
       <c r="N175" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B175, $C$2:$C$706, C175, $D$2:$D$706, D175, $E$2:$E$706, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O175" s="30"/>
@@ -29971,7 +29994,7 @@
         <v>188</v>
       </c>
       <c r="N176" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B176, $C$2:$C$706, C176, $D$2:$D$706, D176, $E$2:$E$706, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="30"/>
@@ -30019,7 +30042,7 @@
         <v>140</v>
       </c>
       <c r="N177" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B177, $C$2:$C$706, C177, $D$2:$D$706, D177, $E$2:$E$706, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O177" s="10"/>
@@ -30066,7 +30089,7 @@
         <v>300</v>
       </c>
       <c r="N178" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B178, $C$2:$C$706, C178, $D$2:$D$706, D178, $E$2:$E$706, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30102,7 +30125,7 @@
         <v>195</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B179, $C$2:$C$706, C179, $D$2:$D$706, D179, $E$2:$E$706, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30136,7 +30159,7 @@
       </c>
       <c r="J180" s="35"/>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B180, $C$2:$C$706, C180, $D$2:$D$706, D180, $E$2:$E$706, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30170,7 +30193,7 @@
       </c>
       <c r="J181" s="35"/>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B181, $C$2:$C$706, C181, $D$2:$D$706, D181, $E$2:$E$706, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P181" s="30"/>
@@ -30217,7 +30240,7 @@
         <v>47480</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B182, $C$2:$C$706, C182, $D$2:$D$706, D182, $E$2:$E$706, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30253,7 +30276,7 @@
         <v>118</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B183, $C$2:$C$706, C183, $D$2:$D$706, D183, $E$2:$E$706, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="39" t="s">
@@ -30290,7 +30313,7 @@
       </c>
       <c r="J184" s="35"/>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B184, $C$2:$C$706, C184, $D$2:$D$706, D184, $E$2:$E$706, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30336,7 +30359,7 @@
         <v>810</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B185, $C$2:$C$706, C185, $D$2:$D$706, D185, $E$2:$E$706, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30382,7 +30405,7 @@
         <v>360</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B186, $C$2:$C$706, C186, $D$2:$D$706, D186, $E$2:$E$706, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30428,7 +30451,7 @@
         <v>340</v>
       </c>
       <c r="N187" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B187, $C$2:$C$706, C187, $D$2:$D$706, D187, $E$2:$E$706, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30464,7 +30487,7 @@
         <v>117</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B188, $C$2:$C$706, C188, $D$2:$D$706, D188, $E$2:$E$706, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30510,7 +30533,7 @@
         <v>250</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B189, $C$2:$C$706, C189, $D$2:$D$706, D189, $E$2:$E$706, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30556,7 +30579,7 @@
         <v>300</v>
       </c>
       <c r="N190" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B190, $C$2:$C$706, C190, $D$2:$D$706, D190, $E$2:$E$706, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30592,7 +30615,7 @@
         <v>118</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B191, $C$2:$C$706, C191, $D$2:$D$706, D191, $E$2:$E$706, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30638,7 +30661,7 @@
         <v>527.5</v>
       </c>
       <c r="N192" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B192, $C$2:$C$706, C192, $D$2:$D$706, D192, $E$2:$E$706, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="30"/>
@@ -30681,7 +30704,7 @@
       <c r="L193" s="28"/>
       <c r="M193" s="28"/>
       <c r="N193" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B193, $C$2:$C$706, C193, $D$2:$D$706, D193, $E$2:$E$706, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="30"/>
@@ -30719,7 +30742,7 @@
         <v>117</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B194, $C$2:$C$706, C194, $D$2:$D$706, D194, $E$2:$E$706, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="10">IF(COUNTIFS( $B$2:$B$706, B194, $C$2:$C$706, C194, $D$2:$D$706, D194, $E$2:$E$706, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -30765,7 +30788,7 @@
         <v>300</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B195, $C$2:$C$706, C195, $D$2:$D$706, D195, $E$2:$E$706, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O195" s="39" t="s">
@@ -30815,7 +30838,7 @@
         <v>300</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B196, $C$2:$C$706, C196, $D$2:$D$706, D196, $E$2:$E$706, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O196" s="10"/>
@@ -30863,7 +30886,7 @@
         <v>816</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B197, $C$2:$C$706, C197, $D$2:$D$706, D197, $E$2:$E$706, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30899,7 +30922,7 @@
         <v>117</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B198, $C$2:$C$706, C198, $D$2:$D$706, D198, $E$2:$E$706, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30945,7 +30968,7 @@
         <v>646</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B199, $C$2:$C$706, C199, $D$2:$D$706, D199, $E$2:$E$706, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="39" t="s">
@@ -30994,7 +31017,7 @@
         <v>260</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B200, $C$2:$C$706, C200, $D$2:$D$706, D200, $E$2:$E$706, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31033,7 +31056,7 @@
       <c r="L201" s="45"/>
       <c r="M201" s="45"/>
       <c r="N201" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B201, $C$2:$C$706, C201, $D$2:$D$706, D201, $E$2:$E$706, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O201" s="24"/>
@@ -31083,7 +31106,7 @@
         <v>880</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B202, $C$2:$C$706, C202, $D$2:$D$706, D202, $E$2:$E$706, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="39" t="s">
@@ -31132,7 +31155,7 @@
         <v>300</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B203, $C$2:$C$706, C203, $D$2:$D$706, D203, $E$2:$E$706, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31178,7 +31201,7 @@
         <v>1000</v>
       </c>
       <c r="N204" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B204, $C$2:$C$706, C204, $D$2:$D$706, D204, $E$2:$E$706, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P204" s="30"/>
@@ -31225,7 +31248,7 @@
         <v>450</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B205, $C$2:$C$706, C205, $D$2:$D$706, D205, $E$2:$E$706, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O205" s="10"/>
@@ -31263,7 +31286,7 @@
         <v>118</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B206, $C$2:$C$706, C206, $D$2:$D$706, D206, $E$2:$E$706, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="30"/>
@@ -31310,7 +31333,7 @@
         <v>250</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B207, $C$2:$C$706, C207, $D$2:$D$706, D207, $E$2:$E$706, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P207" s="30"/>
@@ -31352,7 +31375,7 @@
       <c r="L208" s="17"/>
       <c r="M208" s="17"/>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B208, $C$2:$C$706, C208, $D$2:$D$706, D208, $E$2:$E$706, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31398,7 +31421,7 @@
         <v>651</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B209, $C$2:$C$706, C209, $D$2:$D$706, D209, $E$2:$E$706, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31444,7 +31467,7 @@
         <v>300</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B210, $C$2:$C$706, C210, $D$2:$D$706, D210, $E$2:$E$706, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P210" s="25"/>
@@ -31481,7 +31504,7 @@
         <v>55</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B211, $C$2:$C$706, C211, $D$2:$D$706, D211, $E$2:$E$706, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31517,7 +31540,7 @@
         <v>118</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B212, $C$2:$C$706, C212, $D$2:$D$706, D212, $E$2:$E$706, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31563,7 +31586,7 @@
         <v>400</v>
       </c>
       <c r="N213" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B213, $C$2:$C$706, C213, $D$2:$D$706, D213, $E$2:$E$706, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31599,7 +31622,7 @@
         <v>55</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B214, $C$2:$C$706, C214, $D$2:$D$706, D214, $E$2:$E$706, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31633,7 +31656,7 @@
       </c>
       <c r="J215" s="35"/>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B215, $C$2:$C$706, C215, $D$2:$D$706, D215, $E$2:$E$706, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31667,7 +31690,7 @@
       </c>
       <c r="J216" s="35"/>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B216, $C$2:$C$706, C216, $D$2:$D$706, D216, $E$2:$E$706, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31703,7 +31726,7 @@
         <v>117</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B217, $C$2:$C$706, C217, $D$2:$D$706, D217, $E$2:$E$706, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31739,7 +31762,7 @@
         <v>118</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B218, $C$2:$C$706, C218, $D$2:$D$706, D218, $E$2:$E$706, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31785,7 +31808,7 @@
         <v>940</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B219, $C$2:$C$706, C219, $D$2:$D$706, D219, $E$2:$E$706, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31821,7 +31844,7 @@
         <v>154</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B220, $C$2:$C$706, C220, $D$2:$D$706, D220, $E$2:$E$706, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31855,7 +31878,7 @@
       </c>
       <c r="J221" s="35"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B221, $C$2:$C$706, C221, $D$2:$D$706, D221, $E$2:$E$706, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31891,7 +31914,7 @@
         <v>118</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B222, $C$2:$C$706, C222, $D$2:$D$706, D222, $E$2:$E$706, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O222" s="30"/>
@@ -31926,7 +31949,7 @@
       </c>
       <c r="J223" s="35"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B223, $C$2:$C$706, C223, $D$2:$D$706, D223, $E$2:$E$706, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31962,7 +31985,7 @@
         <v>118</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B224, $C$2:$C$706, C224, $D$2:$D$706, D224, $E$2:$E$706, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32008,7 +32031,7 @@
         <v>650</v>
       </c>
       <c r="N225" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B225, $C$2:$C$706, C225, $D$2:$D$706, D225, $E$2:$E$706, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P225" s="30"/>
@@ -32043,7 +32066,7 @@
       </c>
       <c r="J226" s="35"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B226, $C$2:$C$706, C226, $D$2:$D$706, D226, $E$2:$E$706, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32079,7 +32102,7 @@
         <v>117</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B227, $C$2:$C$706, C227, $D$2:$D$706, D227, $E$2:$E$706, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P227" s="30"/>
@@ -32116,7 +32139,7 @@
         <v>117</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B228, $C$2:$C$706, C228, $D$2:$D$706, D228, $E$2:$E$706, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32150,7 +32173,7 @@
       </c>
       <c r="J229" s="35"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B229, $C$2:$C$706, C229, $D$2:$D$706, D229, $E$2:$E$706, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32186,7 +32209,7 @@
         <v>117</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B230, $C$2:$C$706, C230, $D$2:$D$706, D230, $E$2:$E$706, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32225,7 +32248,7 @@
         <v>146</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B231, $C$2:$C$706, C231, $D$2:$D$706, D231, $E$2:$E$706, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32271,7 +32294,7 @@
         <v>1800</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B232, $C$2:$C$706, C232, $D$2:$D$706, D232, $E$2:$E$706, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32317,7 +32340,7 @@
         <v>370</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B233, $C$2:$C$706, C233, $D$2:$D$706, D233, $E$2:$E$706, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P233" s="30"/>
@@ -32354,7 +32377,7 @@
         <v>117</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B234, $C$2:$C$706, C234, $D$2:$D$706, D234, $E$2:$E$706, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32400,7 +32423,7 @@
         <v>268</v>
       </c>
       <c r="N235" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B235, $C$2:$C$706, C235, $D$2:$D$706, D235, $E$2:$E$706, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32446,7 +32469,7 @@
         <v>320</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B236, $C$2:$C$706, C236, $D$2:$D$706, D236, $E$2:$E$706, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32492,7 +32515,7 @@
         <v>448</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B237, $C$2:$C$706, C237, $D$2:$D$706, D237, $E$2:$E$706, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32528,7 +32551,7 @@
         <v>118</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B238, $C$2:$C$706, C238, $D$2:$D$706, D238, $E$2:$E$706, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32562,7 +32585,7 @@
       </c>
       <c r="J239" s="35"/>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B239, $C$2:$C$706, C239, $D$2:$D$706, D239, $E$2:$E$706, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32608,7 +32631,7 @@
         <v>500</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B240, $C$2:$C$706, C240, $D$2:$D$706, D240, $E$2:$E$706, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O240" s="39" t="s">
@@ -32657,7 +32680,7 @@
         <v>650</v>
       </c>
       <c r="N241" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B241, $C$2:$C$706, C241, $D$2:$D$706, D241, $E$2:$E$706, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P241" s="30"/>
@@ -32704,7 +32727,7 @@
         <v>300</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B242, $C$2:$C$706, C242, $D$2:$D$706, D242, $E$2:$E$706, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32750,7 +32773,7 @@
         <v>300</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B243, $C$2:$C$706, C243, $D$2:$D$706, D243, $E$2:$E$706, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="10"/>
@@ -32789,7 +32812,7 @@
       <c r="L244" s="18"/>
       <c r="M244" s="18"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B244, $C$2:$C$706, C244, $D$2:$D$706, D244, $E$2:$E$706, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P244" s="10"/>
@@ -32836,7 +32859,7 @@
         <v>235</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B245, $C$2:$C$706, C245, $D$2:$D$706, D245, $E$2:$E$706, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32872,7 +32895,7 @@
         <v>118</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B246, $C$2:$C$706, C246, $D$2:$D$706, D246, $E$2:$E$706, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32918,7 +32941,7 @@
         <v>800</v>
       </c>
       <c r="N247" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B247, $C$2:$C$706, C247, $D$2:$D$706, D247, $E$2:$E$706, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32952,7 +32975,7 @@
       </c>
       <c r="J248" s="35"/>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B248, $C$2:$C$706, C248, $D$2:$D$706, D248, $E$2:$E$706, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32986,7 +33009,7 @@
       </c>
       <c r="J249" s="35"/>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B249, $C$2:$C$706, C249, $D$2:$D$706, D249, $E$2:$E$706, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33020,7 +33043,7 @@
       </c>
       <c r="J250" s="35"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B250, $C$2:$C$706, C250, $D$2:$D$706, D250, $E$2:$E$706, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33066,7 +33089,7 @@
         <v>480</v>
       </c>
       <c r="N251" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B251, $C$2:$C$706, C251, $D$2:$D$706, D251, $E$2:$E$706, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33102,7 +33125,7 @@
         <v>117</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B252, $C$2:$C$706, C252, $D$2:$D$706, D252, $E$2:$E$706, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33138,7 +33161,7 @@
         <v>118</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B253, $C$2:$C$706, C253, $D$2:$D$706, D253, $E$2:$E$706, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O253" s="30"/>
@@ -33185,7 +33208,7 @@
         <v>250</v>
       </c>
       <c r="N254" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B254, $C$2:$C$706, C254, $D$2:$D$706, D254, $E$2:$E$706, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33221,7 +33244,7 @@
         <v>117</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B255, $C$2:$C$706, C255, $D$2:$D$706, D255, $E$2:$E$706, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33258,7 +33281,7 @@
       <c r="L256" s="18"/>
       <c r="M256" s="18"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B256, $C$2:$C$706, C256, $D$2:$D$706, D256, $E$2:$E$706, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="10"/>
@@ -33296,7 +33319,7 @@
         <v>118</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B257, $C$2:$C$706, C257, $D$2:$D$706, D257, $E$2:$E$706, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33342,7 +33365,7 @@
         <v>650</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B258, $C$2:$C$706, C258, $D$2:$D$706, D258, $E$2:$E$706, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N297" si="11">IF(COUNTIFS( $B$2:$B$706, B258, $C$2:$C$706, C258, $D$2:$D$706, D258, $E$2:$E$706, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O258" s="30"/>
@@ -33389,7 +33412,7 @@
         <v>300</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B259, $C$2:$C$706, C259, $D$2:$D$706, D259, $E$2:$E$706, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33435,7 +33458,7 @@
         <v>285</v>
       </c>
       <c r="N260" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B260, $C$2:$C$706, C260, $D$2:$D$706, D260, $E$2:$E$706, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="10"/>
@@ -33483,7 +33506,7 @@
         <v>726</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B261, $C$2:$C$706, C261, $D$2:$D$706, D261, $E$2:$E$706, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33517,7 +33540,7 @@
       </c>
       <c r="J262" s="35"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B262, $C$2:$C$706, C262, $D$2:$D$706, D262, $E$2:$E$706, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33553,7 +33576,7 @@
         <v>118</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B263, $C$2:$C$706, C263, $D$2:$D$706, D263, $E$2:$E$706, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33599,7 +33622,7 @@
         <v>260</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B264, $C$2:$C$706, C264, $D$2:$D$706, D264, $E$2:$E$706, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33638,7 +33661,7 @@
       <c r="L265" s="18"/>
       <c r="M265" s="18"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B265, $C$2:$C$706, C265, $D$2:$D$706, D265, $E$2:$E$706, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="10"/>
@@ -33686,7 +33709,7 @@
         <v>300</v>
       </c>
       <c r="N266" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B266, $C$2:$C$706, C266, $D$2:$D$706, D266, $E$2:$E$706, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="10"/>
@@ -33722,7 +33745,7 @@
       </c>
       <c r="J267" s="35"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B267, $C$2:$C$706, C267, $D$2:$D$706, D267, $E$2:$E$706, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33756,7 +33779,7 @@
       </c>
       <c r="J268" s="35"/>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B268, $C$2:$C$706, C268, $D$2:$D$706, D268, $E$2:$E$706, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33793,7 +33816,7 @@
       <c r="L269" s="18"/>
       <c r="M269" s="18"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B269, $C$2:$C$706, C269, $D$2:$D$706, D269, $E$2:$E$706, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P269" s="10"/>
@@ -33830,7 +33853,7 @@
         <v>117</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B270, $C$2:$C$706, C270, $D$2:$D$706, D270, $E$2:$E$706, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33876,7 +33899,7 @@
         <v>275</v>
       </c>
       <c r="N271" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B271, $C$2:$C$706, C271, $D$2:$D$706, D271, $E$2:$E$706, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33913,7 +33936,7 @@
       <c r="L272" s="18"/>
       <c r="M272" s="18"/>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B272, $C$2:$C$706, C272, $D$2:$D$706, D272, $E$2:$E$706, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O272" s="10"/>
@@ -33952,7 +33975,7 @@
       <c r="L273" s="18"/>
       <c r="M273" s="18"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B273, $C$2:$C$706, C273, $D$2:$D$706, D273, $E$2:$E$706, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O273" s="10"/>
@@ -33988,7 +34011,7 @@
       </c>
       <c r="J274" s="35"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B274, $C$2:$C$706, C274, $D$2:$D$706, D274, $E$2:$E$706, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34034,7 +34057,7 @@
         <v>250</v>
       </c>
       <c r="N275" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B275, $C$2:$C$706, C275, $D$2:$D$706, D275, $E$2:$E$706, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P275" s="30"/>
@@ -34071,7 +34094,7 @@
         <v>118</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B276, $C$2:$C$706, C276, $D$2:$D$706, D276, $E$2:$E$706, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34107,7 +34130,7 @@
         <v>118</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B277, $C$2:$C$706, C277, $D$2:$D$706, D277, $E$2:$E$706, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34141,7 +34164,7 @@
       </c>
       <c r="J278" s="35"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B278, $C$2:$C$706, C278, $D$2:$D$706, D278, $E$2:$E$706, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P278" s="30"/>
@@ -34178,7 +34201,7 @@
         <v>118</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B279, $C$2:$C$706, C279, $D$2:$D$706, D279, $E$2:$E$706, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34214,7 +34237,7 @@
         <v>118</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B280, $C$2:$C$706, C280, $D$2:$D$706, D280, $E$2:$E$706, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34248,7 +34271,7 @@
       </c>
       <c r="J281" s="35"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B281, $C$2:$C$706, C281, $D$2:$D$706, D281, $E$2:$E$706, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34282,7 +34305,7 @@
       </c>
       <c r="J282" s="35"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B282, $C$2:$C$706, C282, $D$2:$D$706, D282, $E$2:$E$706, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P282" s="30"/>
@@ -34329,7 +34352,7 @@
         <v>300</v>
       </c>
       <c r="N283" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B283, $C$2:$C$706, C283, $D$2:$D$706, D283, $E$2:$E$706, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34363,7 +34386,7 @@
       </c>
       <c r="J284" s="35"/>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B284, $C$2:$C$706, C284, $D$2:$D$706, D284, $E$2:$E$706, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34409,7 +34432,7 @@
         <v>250</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B285, $C$2:$C$706, C285, $D$2:$D$706, D285, $E$2:$E$706, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34445,7 +34468,7 @@
         <v>55</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B286, $C$2:$C$706, C286, $D$2:$D$706, D286, $E$2:$E$706, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34479,7 +34502,7 @@
       </c>
       <c r="J287" s="35"/>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B287, $C$2:$C$706, C287, $D$2:$D$706, D287, $E$2:$E$706, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34513,7 +34536,7 @@
       </c>
       <c r="J288" s="35"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B288, $C$2:$C$706, C288, $D$2:$D$706, D288, $E$2:$E$706, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34552,7 +34575,7 @@
       <c r="L289" s="18"/>
       <c r="M289" s="18"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B289, $C$2:$C$706, C289, $D$2:$D$706, D289, $E$2:$E$706, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O289" s="10"/>
@@ -34591,7 +34614,7 @@
       <c r="L290" s="18"/>
       <c r="M290" s="18"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B290, $C$2:$C$706, C290, $D$2:$D$706, D290, $E$2:$E$706, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O290" s="10"/>
@@ -34632,7 +34655,7 @@
       <c r="L291" s="28"/>
       <c r="M291" s="28"/>
       <c r="N291" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B291, $C$2:$C$706, C291, $D$2:$D$706, D291, $E$2:$E$706, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O291" s="30"/>
@@ -34673,7 +34696,7 @@
       <c r="L292" s="28"/>
       <c r="M292" s="28"/>
       <c r="N292" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B292, $C$2:$C$706, C292, $D$2:$D$706, D292, $E$2:$E$706, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O292" s="30"/>
@@ -34711,7 +34734,7 @@
         <v>117</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B293, $C$2:$C$706, C293, $D$2:$D$706, D293, $E$2:$E$706, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34749,7 +34772,7 @@
         <v>250</v>
       </c>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B294, $C$2:$C$706, C294, $D$2:$D$706, D294, $E$2:$E$706, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34783,11 +34806,11 @@
         <v>4200</v>
       </c>
       <c r="M295" s="18">
-        <f t="shared" ref="M295:M297" si="7">ABS((D295*E295)-L295)</f>
+        <f t="shared" ref="M295:M297" si="12">ABS((D295*E295)-L295)</f>
         <v>290</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B295, $C$2:$C$706, C295, $D$2:$D$706, D295, $E$2:$E$706, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34821,11 +34844,11 @@
         <v>15300</v>
       </c>
       <c r="M296" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>420</v>
       </c>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B296, $C$2:$C$706, C296, $D$2:$D$706, D296, $E$2:$E$706, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34859,11 +34882,11 @@
         <v>6202</v>
       </c>
       <c r="M297" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>496</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$706, B297, $C$2:$C$706, C297, $D$2:$D$706, D297, $E$2:$E$706, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
